--- a/data/interim/itu_int_bandwidth_processed.xlsx
+++ b/data/interim/itu_int_bandwidth_processed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>int_bandwidth</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>int_bandwidth</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>series_code</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>series_units</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>data_source</t>
         </is>
@@ -1597,7 +1585,7 @@
         <v>2022</v>
       </c>
       <c r="C36" t="n">
-        <v>1089590</v>
+        <v>1089593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2653,7 +2641,7 @@
         <v>2018</v>
       </c>
       <c r="C68" t="n">
-        <v>2081780</v>
+        <v>2081778</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2719,7 +2707,7 @@
         <v>2020</v>
       </c>
       <c r="C70" t="n">
-        <v>2625900</v>
+        <v>2625901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -2752,7 +2740,7 @@
         <v>2021</v>
       </c>
       <c r="C71" t="n">
-        <v>2983570</v>
+        <v>2983565</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2785,7 +2773,7 @@
         <v>2022</v>
       </c>
       <c r="C72" t="n">
-        <v>4168950</v>
+        <v>4168945</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2818,7 +2806,7 @@
         <v>2023</v>
       </c>
       <c r="C73" t="n">
-        <v>3546080</v>
+        <v>3546081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3181,7 +3169,7 @@
         <v>2020</v>
       </c>
       <c r="C84" t="n">
-        <v>1144920</v>
+        <v>1144924</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3280,7 +3268,7 @@
         <v>2023</v>
       </c>
       <c r="C87" t="n">
-        <v>1917270</v>
+        <v>1917273</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3313,7 +3301,7 @@
         <v>2010</v>
       </c>
       <c r="C88" t="n">
-        <v>2676930</v>
+        <v>2676927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3379,7 +3367,7 @@
         <v>2012</v>
       </c>
       <c r="C90" t="n">
-        <v>3686340</v>
+        <v>3686342</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3874,7 +3862,7 @@
         <v>2011</v>
       </c>
       <c r="C105" t="n">
-        <v>1325960</v>
+        <v>1325956</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3907,7 +3895,7 @@
         <v>2012</v>
       </c>
       <c r="C106" t="n">
-        <v>1593270</v>
+        <v>1593271</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -5194,7 +5182,7 @@
         <v>2019</v>
       </c>
       <c r="C145" t="n">
-        <v>1115840</v>
+        <v>1115839</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -5227,7 +5215,7 @@
         <v>2020</v>
       </c>
       <c r="C146" t="n">
-        <v>1672620</v>
+        <v>1672618</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5260,7 +5248,7 @@
         <v>2021</v>
       </c>
       <c r="C147" t="n">
-        <v>1911440</v>
+        <v>1911442</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -5293,7 +5281,7 @@
         <v>2022</v>
       </c>
       <c r="C148" t="n">
-        <v>2198290</v>
+        <v>2198292</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -5326,7 +5314,7 @@
         <v>2023</v>
       </c>
       <c r="C149" t="n">
-        <v>2720620</v>
+        <v>2720622</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -7141,7 +7129,7 @@
         <v>2019</v>
       </c>
       <c r="C204" t="n">
-        <v>1068100</v>
+        <v>1068098</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7372,7 +7360,7 @@
         <v>2012</v>
       </c>
       <c r="C211" t="n">
-        <v>2044310</v>
+        <v>2044313</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -7405,7 +7393,7 @@
         <v>2013</v>
       </c>
       <c r="C212" t="n">
-        <v>3205940</v>
+        <v>3205939</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -8626,7 +8614,7 @@
         <v>2021</v>
       </c>
       <c r="C249" t="n">
-        <v>1424890</v>
+        <v>1424888</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -8659,7 +8647,7 @@
         <v>2022</v>
       </c>
       <c r="C250" t="n">
-        <v>1606800</v>
+        <v>1606802</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -8692,7 +8680,7 @@
         <v>2023</v>
       </c>
       <c r="C251" t="n">
-        <v>1989480</v>
+        <v>1989482</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -11629,7 +11617,7 @@
         <v>2010</v>
       </c>
       <c r="C340" t="n">
-        <v>3598.33</v>
+        <v>3598.33481060552</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -11662,7 +11650,7 @@
         <v>2011</v>
       </c>
       <c r="C341" t="n">
-        <v>8911.25</v>
+        <v>8911.25044513492</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -11695,7 +11683,7 @@
         <v>2012</v>
       </c>
       <c r="C342" t="n">
-        <v>10265.1</v>
+        <v>10265.0855697533</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -11728,7 +11716,7 @@
         <v>2013</v>
       </c>
       <c r="C343" t="n">
-        <v>15603</v>
+        <v>15602.9834546785</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -11761,7 +11749,7 @@
         <v>2014</v>
       </c>
       <c r="C344" t="n">
-        <v>21053.8</v>
+        <v>21053.7697841037</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -11794,7 +11782,7 @@
         <v>2015</v>
       </c>
       <c r="C345" t="n">
-        <v>40458.7</v>
+        <v>40458.6918218239</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -11827,7 +11815,7 @@
         <v>2016</v>
       </c>
       <c r="C346" t="n">
-        <v>38047.9</v>
+        <v>38047.9191227333</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -11860,7 +11848,7 @@
         <v>2017</v>
       </c>
       <c r="C347" t="n">
-        <v>71387.5</v>
+        <v>71387.5270457978</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -11893,7 +11881,7 @@
         <v>2018</v>
       </c>
       <c r="C348" t="n">
-        <v>117267</v>
+        <v>117267.389813967</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -11926,7 +11914,7 @@
         <v>2019</v>
       </c>
       <c r="C349" t="n">
-        <v>228157</v>
+        <v>228157.158540096</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -11959,7 +11947,7 @@
         <v>2020</v>
       </c>
       <c r="C350" t="n">
-        <v>204424</v>
+        <v>204424.101626764</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -11992,7 +11980,7 @@
         <v>2021</v>
       </c>
       <c r="C351" t="n">
-        <v>166346</v>
+        <v>166345.625566786</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -12025,7 +12013,7 @@
         <v>2022</v>
       </c>
       <c r="C352" t="n">
-        <v>150145</v>
+        <v>150145.407261824</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -12058,7 +12046,7 @@
         <v>2023</v>
       </c>
       <c r="C353" t="n">
-        <v>155944</v>
+        <v>155944.177349066</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -12091,7 +12079,7 @@
         <v>2010</v>
       </c>
       <c r="C354" t="n">
-        <v>41306.2</v>
+        <v>41306.1804938906</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -12124,7 +12112,7 @@
         <v>2011</v>
       </c>
       <c r="C355" t="n">
-        <v>50924.3</v>
+        <v>50924.252406988</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -12157,7 +12145,7 @@
         <v>2012</v>
       </c>
       <c r="C356" t="n">
-        <v>60554</v>
+        <v>60553.9801990156</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -12190,7 +12178,7 @@
         <v>2013</v>
       </c>
       <c r="C357" t="n">
-        <v>85851.10000000001</v>
+        <v>85851.0959149933</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -12223,7 +12211,7 @@
         <v>2014</v>
       </c>
       <c r="C358" t="n">
-        <v>38606.3</v>
+        <v>38606.348264124</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -12256,7 +12244,7 @@
         <v>2015</v>
       </c>
       <c r="C359" t="n">
-        <v>41647.2</v>
+        <v>41647.1975658601</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -12289,7 +12277,7 @@
         <v>2016</v>
       </c>
       <c r="C360" t="n">
-        <v>45205.3</v>
+        <v>45205.2921091588</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -12322,7 +12310,7 @@
         <v>2017</v>
       </c>
       <c r="C361" t="n">
-        <v>46029.1</v>
+        <v>46029.1190435763</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -12355,7 +12343,7 @@
         <v>2010</v>
       </c>
       <c r="C362" t="n">
-        <v>4154.44</v>
+        <v>4154.43522584986</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -12388,7 +12376,7 @@
         <v>2011</v>
       </c>
       <c r="C363" t="n">
-        <v>6698.25</v>
+        <v>6698.24927210557</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -12421,7 +12409,7 @@
         <v>2012</v>
       </c>
       <c r="C364" t="n">
-        <v>10025.4</v>
+        <v>10025.4037331404</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -12454,7 +12442,7 @@
         <v>2013</v>
       </c>
       <c r="C365" t="n">
-        <v>15045.6</v>
+        <v>15045.6488141451</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -12487,7 +12475,7 @@
         <v>2014</v>
       </c>
       <c r="C366" t="n">
-        <v>19416.2</v>
+        <v>19416.1894471868</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -12520,7 +12508,7 @@
         <v>2015</v>
       </c>
       <c r="C367" t="n">
-        <v>26658.9</v>
+        <v>26658.8740727069</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -12553,7 +12541,7 @@
         <v>2016</v>
       </c>
       <c r="C368" t="n">
-        <v>26346.6</v>
+        <v>26346.6481186264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -12586,7 +12574,7 @@
         <v>2017</v>
       </c>
       <c r="C369" t="n">
-        <v>36113.7</v>
+        <v>36113.7221109273</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -12619,7 +12607,7 @@
         <v>2018</v>
       </c>
       <c r="C370" t="n">
-        <v>41235.9</v>
+        <v>41235.946908818</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -12652,7 +12640,7 @@
         <v>2019</v>
       </c>
       <c r="C371" t="n">
-        <v>47975</v>
+        <v>47974.9962291584</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -12685,7 +12673,7 @@
         <v>2020</v>
       </c>
       <c r="C372" t="n">
-        <v>67572</v>
+        <v>67572.0137933337</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -12718,7 +12706,7 @@
         <v>2021</v>
       </c>
       <c r="C373" t="n">
-        <v>67627.2</v>
+        <v>67627.2142176593</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -12751,7 +12739,7 @@
         <v>2022</v>
       </c>
       <c r="C374" t="n">
-        <v>105834</v>
+        <v>105833.98023021</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -12784,7 +12772,7 @@
         <v>2023</v>
       </c>
       <c r="C375" t="n">
-        <v>234930</v>
+        <v>234930.351755882</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -12817,7 +12805,7 @@
         <v>2010</v>
       </c>
       <c r="C376" t="n">
-        <v>57663.8</v>
+        <v>57663.7621145681</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -12850,7 +12838,7 @@
         <v>2011</v>
       </c>
       <c r="C377" t="n">
-        <v>71323.60000000001</v>
+        <v>71323.6088786734</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -12883,7 +12871,7 @@
         <v>2012</v>
       </c>
       <c r="C378" t="n">
-        <v>77106.3</v>
+        <v>77106.334646498</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -12916,7 +12904,7 @@
         <v>2013</v>
       </c>
       <c r="C379" t="n">
-        <v>82435.2</v>
+        <v>82435.2372647415</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -12949,7 +12937,7 @@
         <v>2014</v>
       </c>
       <c r="C380" t="n">
-        <v>92773.3</v>
+        <v>92773.32381574179</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -12982,7 +12970,7 @@
         <v>2015</v>
       </c>
       <c r="C381" t="n">
-        <v>100219</v>
+        <v>100218.751815356</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -13015,7 +13003,7 @@
         <v>2016</v>
       </c>
       <c r="C382" t="n">
-        <v>113830</v>
+        <v>113829.880449506</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -13048,7 +13036,7 @@
         <v>2017</v>
       </c>
       <c r="C383" t="n">
-        <v>118665</v>
+        <v>118664.825574573</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -13081,7 +13069,7 @@
         <v>2010</v>
       </c>
       <c r="C384" t="n">
-        <v>7059.5</v>
+        <v>7059.50382013986</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -13114,7 +13102,7 @@
         <v>2011</v>
       </c>
       <c r="C385" t="n">
-        <v>21113.2</v>
+        <v>21113.2265391146</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -13147,7 +13135,7 @@
         <v>2012</v>
       </c>
       <c r="C386" t="n">
-        <v>36985.9</v>
+        <v>36985.8595661707</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -13180,7 +13168,7 @@
         <v>2013</v>
       </c>
       <c r="C387" t="n">
-        <v>50766.8</v>
+        <v>50766.800786057</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -13213,7 +13201,7 @@
         <v>2014</v>
       </c>
       <c r="C388" t="n">
-        <v>82658.5</v>
+        <v>82658.5175010145</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -13246,7 +13234,7 @@
         <v>2015</v>
       </c>
       <c r="C389" t="n">
-        <v>84652.2</v>
+        <v>84652.17633733879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -13279,7 +13267,7 @@
         <v>2016</v>
       </c>
       <c r="C390" t="n">
-        <v>116230</v>
+        <v>116230.399121429</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -13312,7 +13300,7 @@
         <v>2017</v>
       </c>
       <c r="C391" t="n">
-        <v>140921</v>
+        <v>140921.397798393</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -13345,7 +13333,7 @@
         <v>2018</v>
       </c>
       <c r="C392" t="n">
-        <v>156147</v>
+        <v>156147.168717064</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -13378,7 +13366,7 @@
         <v>2019</v>
       </c>
       <c r="C393" t="n">
-        <v>164406</v>
+        <v>164406.05340367</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -13411,7 +13399,7 @@
         <v>2020</v>
       </c>
       <c r="C394" t="n">
-        <v>206713</v>
+        <v>206712.819582707</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -13444,7 +13432,7 @@
         <v>2021</v>
       </c>
       <c r="C395" t="n">
-        <v>204402</v>
+        <v>204402.269286748</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -13477,7 +13465,7 @@
         <v>2022</v>
       </c>
       <c r="C396" t="n">
-        <v>250402</v>
+        <v>250402.338890841</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -13510,7 +13498,7 @@
         <v>2023</v>
       </c>
       <c r="C397" t="n">
-        <v>339525</v>
+        <v>339524.86265424</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -13543,7 +13531,7 @@
         <v>2010</v>
       </c>
       <c r="C398" t="n">
-        <v>31273.5</v>
+        <v>31273.5333001954</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -13576,7 +13564,7 @@
         <v>2011</v>
       </c>
       <c r="C399" t="n">
-        <v>34254.6</v>
+        <v>34254.6265087178</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -13609,7 +13597,7 @@
         <v>2012</v>
       </c>
       <c r="C400" t="n">
-        <v>46857.2</v>
+        <v>46857.2289187912</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -13642,7 +13630,7 @@
         <v>2013</v>
       </c>
       <c r="C401" t="n">
-        <v>56902</v>
+        <v>56901.9629435895</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -13675,7 +13663,7 @@
         <v>2014</v>
       </c>
       <c r="C402" t="n">
-        <v>74398.7</v>
+        <v>74398.67021972471</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -13708,7 +13696,7 @@
         <v>2015</v>
       </c>
       <c r="C403" t="n">
-        <v>86075.89999999999</v>
+        <v>86075.86718359571</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -13741,7 +13729,7 @@
         <v>2016</v>
       </c>
       <c r="C404" t="n">
-        <v>124193</v>
+        <v>124193.363277724</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -13774,7 +13762,7 @@
         <v>2017</v>
       </c>
       <c r="C405" t="n">
-        <v>113896</v>
+        <v>113896.475171985</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -13807,7 +13795,7 @@
         <v>2018</v>
       </c>
       <c r="C406" t="n">
-        <v>296349</v>
+        <v>296349.26249992</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -13840,7 +13828,7 @@
         <v>2019</v>
       </c>
       <c r="C407" t="n">
-        <v>330580</v>
+        <v>330579.922296264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -13873,7 +13861,7 @@
         <v>2020</v>
       </c>
       <c r="C408" t="n">
-        <v>378718</v>
+        <v>378718.31467746</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -13906,7 +13894,7 @@
         <v>2021</v>
       </c>
       <c r="C409" t="n">
-        <v>433833</v>
+        <v>433832.686875884</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -13939,7 +13927,7 @@
         <v>2022</v>
       </c>
       <c r="C410" t="n">
-        <v>610757</v>
+        <v>610757.114410718</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -13972,7 +13960,7 @@
         <v>2023</v>
       </c>
       <c r="C411" t="n">
-        <v>521805</v>
+        <v>521804.560844392</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -14005,7 +13993,7 @@
         <v>2010</v>
       </c>
       <c r="C412" t="n">
-        <v>35960.9</v>
+        <v>35960.9430816861</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -14038,7 +14026,7 @@
         <v>2011</v>
       </c>
       <c r="C413" t="n">
-        <v>40023.2</v>
+        <v>40023.2018561485</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -14071,7 +14059,7 @@
         <v>2012</v>
       </c>
       <c r="C414" t="n">
-        <v>55626.4</v>
+        <v>55626.3761733689</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -14104,7 +14092,7 @@
         <v>2013</v>
       </c>
       <c r="C415" t="n">
-        <v>55046.5</v>
+        <v>55046.511627907</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -14137,7 +14125,7 @@
         <v>2014</v>
       </c>
       <c r="C416" t="n">
-        <v>31366.2</v>
+        <v>31366.1710037175</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -14170,7 +14158,7 @@
         <v>2015</v>
       </c>
       <c r="C417" t="n">
-        <v>39361</v>
+        <v>39360.9631859227</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -14203,7 +14191,7 @@
         <v>2016</v>
       </c>
       <c r="C418" t="n">
-        <v>45074.1</v>
+        <v>45074.1464536154</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -14236,7 +14224,7 @@
         <v>2017</v>
       </c>
       <c r="C419" t="n">
-        <v>225637</v>
+        <v>225637.377646255</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -14269,7 +14257,7 @@
         <v>2018</v>
       </c>
       <c r="C420" t="n">
-        <v>264508</v>
+        <v>264507.97573579</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -14302,7 +14290,7 @@
         <v>2019</v>
       </c>
       <c r="C421" t="n">
-        <v>971013</v>
+        <v>971012.854609929</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -14335,7 +14323,7 @@
         <v>2020</v>
       </c>
       <c r="C422" t="n">
-        <v>1251970</v>
+        <v>1251967.19518863</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -14368,7 +14356,7 @@
         <v>2021</v>
       </c>
       <c r="C423" t="n">
-        <v>1414180</v>
+        <v>1414175.09141751</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -14401,7 +14389,7 @@
         <v>2022</v>
       </c>
       <c r="C424" t="n">
-        <v>1910610</v>
+        <v>1910610.05162786</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -14434,7 +14422,7 @@
         <v>2023</v>
       </c>
       <c r="C425" t="n">
-        <v>1983930</v>
+        <v>1983933.15397351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -14467,7 +14455,7 @@
         <v>2010</v>
       </c>
       <c r="C426" t="n">
-        <v>33117.6</v>
+        <v>33117.6097900353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -14500,7 +14488,7 @@
         <v>2011</v>
       </c>
       <c r="C427" t="n">
-        <v>39752.7</v>
+        <v>39752.7147448868</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -14533,7 +14521,7 @@
         <v>2012</v>
       </c>
       <c r="C428" t="n">
-        <v>45557.4</v>
+        <v>45557.4204434973</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -14566,7 +14554,7 @@
         <v>2013</v>
       </c>
       <c r="C429" t="n">
-        <v>28997.5</v>
+        <v>28997.4596004308</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -14599,7 +14587,7 @@
         <v>2014</v>
       </c>
       <c r="C430" t="n">
-        <v>31950.4</v>
+        <v>31950.4208116193</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -14632,7 +14620,7 @@
         <v>2015</v>
       </c>
       <c r="C431" t="n">
-        <v>37160</v>
+        <v>37159.978581232</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -14665,7 +14653,7 @@
         <v>2016</v>
       </c>
       <c r="C432" t="n">
-        <v>42290.9</v>
+        <v>42290.9096946256</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -14698,7 +14686,7 @@
         <v>2017</v>
       </c>
       <c r="C433" t="n">
-        <v>45124.2</v>
+        <v>45124.17794728</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -14731,7 +14719,7 @@
         <v>2010</v>
       </c>
       <c r="C434" t="n">
-        <v>81823.89999999999</v>
+        <v>81823.9383344542</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -14764,7 +14752,7 @@
         <v>2011</v>
       </c>
       <c r="C435" t="n">
-        <v>91304.2</v>
+        <v>91304.2159283082</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -14797,7 +14785,7 @@
         <v>2012</v>
       </c>
       <c r="C436" t="n">
-        <v>106194</v>
+        <v>106193.815108486</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -14830,7 +14818,7 @@
         <v>2013</v>
       </c>
       <c r="C437" t="n">
-        <v>54315.6</v>
+        <v>54315.5677499447</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -14863,7 +14851,7 @@
         <v>2014</v>
       </c>
       <c r="C438" t="n">
-        <v>62015</v>
+        <v>62015.0203923106</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -14896,7 +14884,7 @@
         <v>2015</v>
       </c>
       <c r="C439" t="n">
-        <v>69497</v>
+        <v>69496.97037194599</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -14929,7 +14917,7 @@
         <v>2016</v>
       </c>
       <c r="C440" t="n">
-        <v>78558.7</v>
+        <v>78558.69582788731</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -14962,7 +14950,7 @@
         <v>2017</v>
       </c>
       <c r="C441" t="n">
-        <v>84125.89999999999</v>
+        <v>84125.9092536419</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -14995,7 +14983,7 @@
         <v>2010</v>
       </c>
       <c r="C442" t="n">
-        <v>20856.2</v>
+        <v>20856.2377607176</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -15028,7 +15016,7 @@
         <v>2011</v>
       </c>
       <c r="C443" t="n">
-        <v>28213</v>
+        <v>28213.0045287205</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -15061,7 +15049,7 @@
         <v>2012</v>
       </c>
       <c r="C444" t="n">
-        <v>33886.2</v>
+        <v>33886.172418357</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -15094,7 +15082,7 @@
         <v>2013</v>
       </c>
       <c r="C445" t="n">
-        <v>12804</v>
+        <v>12803.9910210733</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -15127,7 +15115,7 @@
         <v>2014</v>
       </c>
       <c r="C446" t="n">
-        <v>14982.8</v>
+        <v>14982.816421886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -15160,7 +15148,7 @@
         <v>2015</v>
       </c>
       <c r="C447" t="n">
-        <v>17779.2</v>
+        <v>17779.2302004602</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -15193,7 +15181,7 @@
         <v>2016</v>
       </c>
       <c r="C448" t="n">
-        <v>21612.2</v>
+        <v>21612.2429376165</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -15226,7 +15214,7 @@
         <v>2017</v>
       </c>
       <c r="C449" t="n">
-        <v>22616.4</v>
+        <v>22616.4231589101</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -15259,7 +15247,7 @@
         <v>2010</v>
       </c>
       <c r="C450" t="n">
-        <v>17274.4</v>
+        <v>17274.4260384183</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -15292,7 +15280,7 @@
         <v>2011</v>
       </c>
       <c r="C451" t="n">
-        <v>18834.4</v>
+        <v>18834.4063922469</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -15325,7 +15313,7 @@
         <v>2012</v>
       </c>
       <c r="C452" t="n">
-        <v>20414.1</v>
+        <v>20414.0884429041</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -15358,7 +15346,7 @@
         <v>2013</v>
       </c>
       <c r="C453" t="n">
-        <v>22763.2</v>
+        <v>22763.1591926363</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -15391,7 +15379,7 @@
         <v>2014</v>
       </c>
       <c r="C454" t="n">
-        <v>30126.6</v>
+        <v>30126.6231098587</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -15424,7 +15412,7 @@
         <v>2015</v>
       </c>
       <c r="C455" t="n">
-        <v>94327</v>
+        <v>94326.9921252176</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -15457,7 +15445,7 @@
         <v>2016</v>
       </c>
       <c r="C456" t="n">
-        <v>106395</v>
+        <v>106395.186681755</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -15490,7 +15478,7 @@
         <v>2017</v>
       </c>
       <c r="C457" t="n">
-        <v>107786</v>
+        <v>107786.021974685</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -15523,7 +15511,7 @@
         <v>2010</v>
       </c>
       <c r="C458" t="n">
-        <v>55189.9</v>
+        <v>55189.9327633664</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -15556,7 +15544,7 @@
         <v>2011</v>
       </c>
       <c r="C459" t="n">
-        <v>61945.2</v>
+        <v>61945.1754757921</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -15589,7 +15577,7 @@
         <v>2012</v>
       </c>
       <c r="C460" t="n">
-        <v>69519.3</v>
+        <v>69519.3055281609</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -15622,7 +15610,7 @@
         <v>2013</v>
       </c>
       <c r="C461" t="n">
-        <v>30285.3</v>
+        <v>30285.2714152046</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -15655,7 +15643,7 @@
         <v>2014</v>
       </c>
       <c r="C462" t="n">
-        <v>33234.1</v>
+        <v>33234.1497490288</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -15688,7 +15676,7 @@
         <v>2015</v>
       </c>
       <c r="C463" t="n">
-        <v>36970.7</v>
+        <v>36970.6632857406</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -15721,7 +15709,7 @@
         <v>2016</v>
       </c>
       <c r="C464" t="n">
-        <v>41483</v>
+        <v>41483.0306365241</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -15754,7 +15742,7 @@
         <v>2017</v>
       </c>
       <c r="C465" t="n">
-        <v>43654.9</v>
+        <v>43654.8943661842</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -15787,7 +15775,7 @@
         <v>2010</v>
       </c>
       <c r="C466" t="n">
-        <v>59009.4</v>
+        <v>59009.3877893481</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -15820,7 +15808,7 @@
         <v>2011</v>
       </c>
       <c r="C467" t="n">
-        <v>72927.10000000001</v>
+        <v>72927.1389308682</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -15853,7 +15841,7 @@
         <v>2012</v>
       </c>
       <c r="C468" t="n">
-        <v>87579.7</v>
+        <v>87579.7081292087</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -15886,7 +15874,7 @@
         <v>2013</v>
       </c>
       <c r="C469" t="n">
-        <v>46883.2</v>
+        <v>46883.1614621148</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -15919,7 +15907,7 @@
         <v>2014</v>
       </c>
       <c r="C470" t="n">
-        <v>55843.6</v>
+        <v>55843.5823090461</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -15952,7 +15940,7 @@
         <v>2015</v>
       </c>
       <c r="C471" t="n">
-        <v>62959.5</v>
+        <v>62959.4557529157</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -15985,7 +15973,7 @@
         <v>2016</v>
       </c>
       <c r="C472" t="n">
-        <v>70057.7</v>
+        <v>70057.71481924471</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -16018,7 +16006,7 @@
         <v>2017</v>
       </c>
       <c r="C473" t="n">
-        <v>73524.10000000001</v>
+        <v>73524.1257164518</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -16051,7 +16039,7 @@
         <v>2010</v>
       </c>
       <c r="C474" t="n">
-        <v>14053.4</v>
+        <v>14053.3606839574</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -16084,7 +16072,7 @@
         <v>2011</v>
       </c>
       <c r="C475" t="n">
-        <v>27005.5</v>
+        <v>27005.5102043021</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -16117,7 +16105,7 @@
         <v>2012</v>
       </c>
       <c r="C476" t="n">
-        <v>36204.7</v>
+        <v>36204.6715249715</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -16150,7 +16138,7 @@
         <v>2013</v>
       </c>
       <c r="C477" t="n">
-        <v>43765.5</v>
+        <v>43765.5116826563</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -16183,7 +16171,7 @@
         <v>2014</v>
       </c>
       <c r="C478" t="n">
-        <v>50490.4</v>
+        <v>50490.3716697239</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -16216,7 +16204,7 @@
         <v>2015</v>
       </c>
       <c r="C479" t="n">
-        <v>51089.4</v>
+        <v>51089.3591782497</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -16249,7 +16237,7 @@
         <v>2016</v>
       </c>
       <c r="C480" t="n">
-        <v>48979.6</v>
+        <v>48979.6115337157</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -16282,7 +16270,7 @@
         <v>2017</v>
       </c>
       <c r="C481" t="n">
-        <v>61981.9</v>
+        <v>61981.862147073</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -16315,7 +16303,7 @@
         <v>2018</v>
       </c>
       <c r="C482" t="n">
-        <v>82475.39999999999</v>
+        <v>82475.43250092911</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -16348,7 +16336,7 @@
         <v>2019</v>
       </c>
       <c r="C483" t="n">
-        <v>104103</v>
+        <v>104103.28760089</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -16381,7 +16369,7 @@
         <v>2020</v>
       </c>
       <c r="C484" t="n">
-        <v>156329</v>
+        <v>156328.658260127</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -16414,7 +16402,7 @@
         <v>2021</v>
       </c>
       <c r="C485" t="n">
-        <v>180673</v>
+        <v>180673.092201085</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -16447,7 +16435,7 @@
         <v>2022</v>
       </c>
       <c r="C486" t="n">
-        <v>211121</v>
+        <v>211120.885706383</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -16480,7 +16468,7 @@
         <v>2023</v>
       </c>
       <c r="C487" t="n">
-        <v>265610</v>
+        <v>265610.313008767</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -16513,7 +16501,7 @@
         <v>2010</v>
       </c>
       <c r="C488" t="n">
-        <v>39609.4</v>
+        <v>39609.3687134418</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -16546,7 +16534,7 @@
         <v>2011</v>
       </c>
       <c r="C489" t="n">
-        <v>49780.5</v>
+        <v>49780.5498037736</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -16579,7 +16567,7 @@
         <v>2012</v>
       </c>
       <c r="C490" t="n">
-        <v>51090.6</v>
+        <v>51090.5779114523</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -16612,7 +16600,7 @@
         <v>2013</v>
       </c>
       <c r="C491" t="n">
-        <v>28313.3</v>
+        <v>28313.2979673277</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -16645,7 +16633,7 @@
         <v>2014</v>
       </c>
       <c r="C492" t="n">
-        <v>31938.1</v>
+        <v>31938.0559883247</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -16678,7 +16666,7 @@
         <v>2015</v>
       </c>
       <c r="C493" t="n">
-        <v>37096.5</v>
+        <v>37096.4704385341</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -16711,7 +16699,7 @@
         <v>2016</v>
       </c>
       <c r="C494" t="n">
-        <v>43320.8</v>
+        <v>43320.790350615</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -16744,7 +16732,7 @@
         <v>2017</v>
       </c>
       <c r="C495" t="n">
-        <v>46496.9</v>
+        <v>46496.8743881318</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -16777,7 +16765,7 @@
         <v>2010</v>
       </c>
       <c r="C496" t="n">
-        <v>138690</v>
+        <v>138689.846036979</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -16810,7 +16798,7 @@
         <v>2011</v>
       </c>
       <c r="C497" t="n">
-        <v>148359</v>
+        <v>148358.645988795</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -16843,7 +16831,7 @@
         <v>2012</v>
       </c>
       <c r="C498" t="n">
-        <v>177355</v>
+        <v>177355.341002888</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -16876,7 +16864,7 @@
         <v>2013</v>
       </c>
       <c r="C499" t="n">
-        <v>82512.8</v>
+        <v>82512.8073137938</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -16909,7 +16897,7 @@
         <v>2014</v>
       </c>
       <c r="C500" t="n">
-        <v>91015.39999999999</v>
+        <v>91015.3787217436</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -16942,7 +16930,7 @@
         <v>2015</v>
       </c>
       <c r="C501" t="n">
-        <v>99372</v>
+        <v>99372.00981585019</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -16975,7 +16963,7 @@
         <v>2016</v>
       </c>
       <c r="C502" t="n">
-        <v>104623</v>
+        <v>104622.616631404</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -17008,7 +16996,7 @@
         <v>2017</v>
       </c>
       <c r="C503" t="n">
-        <v>109729</v>
+        <v>109729.101948154</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -17041,7 +17029,7 @@
         <v>2010</v>
       </c>
       <c r="C504" t="n">
-        <v>12787.3</v>
+        <v>12787.2926860173</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -17074,7 +17062,7 @@
         <v>2011</v>
       </c>
       <c r="C505" t="n">
-        <v>14483.2</v>
+        <v>14483.1929553749</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -17107,7 +17095,7 @@
         <v>2012</v>
       </c>
       <c r="C506" t="n">
-        <v>23478.4</v>
+        <v>23478.3890819856</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -17140,7 +17128,7 @@
         <v>2013</v>
       </c>
       <c r="C507" t="n">
-        <v>27343</v>
+        <v>27343.0262790054</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -17173,7 +17161,7 @@
         <v>2014</v>
       </c>
       <c r="C508" t="n">
-        <v>35549.4</v>
+        <v>35549.4126170553</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -17206,7 +17194,7 @@
         <v>2015</v>
       </c>
       <c r="C509" t="n">
-        <v>40496.2</v>
+        <v>40496.1698044974</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -17239,7 +17227,7 @@
         <v>2016</v>
       </c>
       <c r="C510" t="n">
-        <v>54285</v>
+        <v>54285.0332314423</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -17272,7 +17260,7 @@
         <v>2017</v>
       </c>
       <c r="C511" t="n">
-        <v>86606.2</v>
+        <v>86606.197293587</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -17305,7 +17293,7 @@
         <v>2018</v>
       </c>
       <c r="C512" t="n">
-        <v>107064</v>
+        <v>107064.380744909</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -17338,7 +17326,7 @@
         <v>2019</v>
       </c>
       <c r="C513" t="n">
-        <v>140394</v>
+        <v>140393.905779094</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -17371,7 +17359,7 @@
         <v>2020</v>
       </c>
       <c r="C514" t="n">
-        <v>179489</v>
+        <v>179488.502406955</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -17404,7 +17392,7 @@
         <v>2021</v>
       </c>
       <c r="C515" t="n">
-        <v>221007</v>
+        <v>221007.437681706</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -17437,7 +17425,7 @@
         <v>2022</v>
       </c>
       <c r="C516" t="n">
-        <v>218551</v>
+        <v>218551.343515159</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -17470,7 +17458,7 @@
         <v>2010</v>
       </c>
       <c r="C517" t="n">
-        <v>33242.4</v>
+        <v>33242.3528917431</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -17503,7 +17491,7 @@
         <v>2011</v>
       </c>
       <c r="C518" t="n">
-        <v>34786.7</v>
+        <v>34786.7110788055</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -17536,7 +17524,7 @@
         <v>2012</v>
       </c>
       <c r="C519" t="n">
-        <v>41300.8</v>
+        <v>41300.8000873595</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -17569,7 +17557,7 @@
         <v>2013</v>
       </c>
       <c r="C520" t="n">
-        <v>13189.6</v>
+        <v>13189.595756696</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -17602,7 +17590,7 @@
         <v>2014</v>
       </c>
       <c r="C521" t="n">
-        <v>14835.8</v>
+        <v>14835.7751398268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -17635,7 +17623,7 @@
         <v>2015</v>
       </c>
       <c r="C522" t="n">
-        <v>16508.4</v>
+        <v>16508.37446725</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -17668,7 +17656,7 @@
         <v>2016</v>
       </c>
       <c r="C523" t="n">
-        <v>19841.9</v>
+        <v>19841.8908845808</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -17701,7 +17689,7 @@
         <v>2017</v>
       </c>
       <c r="C524" t="n">
-        <v>21526.6</v>
+        <v>21526.6294838851</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -17734,7 +17722,7 @@
         <v>2010</v>
       </c>
       <c r="C525" t="n">
-        <v>47898.9</v>
+        <v>47898.9182027953</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -17767,7 +17755,7 @@
         <v>2011</v>
       </c>
       <c r="C526" t="n">
-        <v>61511.2</v>
+        <v>61511.2404964449</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -17800,7 +17788,7 @@
         <v>2012</v>
       </c>
       <c r="C527" t="n">
-        <v>64585.1</v>
+        <v>64585.1032100818</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -17833,7 +17821,7 @@
         <v>2013</v>
       </c>
       <c r="C528" t="n">
-        <v>46489.6</v>
+        <v>46489.6427562866</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -17866,7 +17854,7 @@
         <v>2014</v>
       </c>
       <c r="C529" t="n">
-        <v>55815.1</v>
+        <v>55815.0837687804</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -17899,7 +17887,7 @@
         <v>2015</v>
       </c>
       <c r="C530" t="n">
-        <v>62732.8</v>
+        <v>62732.7624722833</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -17932,7 +17920,7 @@
         <v>2016</v>
       </c>
       <c r="C531" t="n">
-        <v>63111.4</v>
+        <v>63111.3517757325</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -17965,7 +17953,7 @@
         <v>2017</v>
       </c>
       <c r="C532" t="n">
-        <v>65485</v>
+        <v>65485.0121438317</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -17998,7 +17986,7 @@
         <v>2010</v>
       </c>
       <c r="C533" t="n">
-        <v>30276.1</v>
+        <v>30276.1385793422</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -18031,7 +18019,7 @@
         <v>2011</v>
       </c>
       <c r="C534" t="n">
-        <v>48229.5</v>
+        <v>48229.536538158</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -18064,7 +18052,7 @@
         <v>2012</v>
       </c>
       <c r="C535" t="n">
-        <v>50438.6</v>
+        <v>50438.5561295292</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -18097,7 +18085,7 @@
         <v>2013</v>
       </c>
       <c r="C536" t="n">
-        <v>61362.4</v>
+        <v>61362.3764518179</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -18130,7 +18118,7 @@
         <v>2014</v>
       </c>
       <c r="C537" t="n">
-        <v>84648.10000000001</v>
+        <v>84648.06652738609</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -18163,7 +18151,7 @@
         <v>2015</v>
       </c>
       <c r="C538" t="n">
-        <v>102358</v>
+        <v>102358.278235948</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -18196,7 +18184,7 @@
         <v>2016</v>
       </c>
       <c r="C539" t="n">
-        <v>153816</v>
+        <v>153815.643178547</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -18229,7 +18217,7 @@
         <v>2017</v>
       </c>
       <c r="C540" t="n">
-        <v>212984</v>
+        <v>212983.50518306</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -18262,7 +18250,7 @@
         <v>2018</v>
       </c>
       <c r="C541" t="n">
-        <v>279203</v>
+        <v>279202.905428696</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -18295,7 +18283,7 @@
         <v>2019</v>
       </c>
       <c r="C542" t="n">
-        <v>382138</v>
+        <v>382138.045078134</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -18328,7 +18316,7 @@
         <v>2020</v>
       </c>
       <c r="C543" t="n">
-        <v>576304</v>
+        <v>576303.80235821</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -18361,7 +18349,7 @@
         <v>2021</v>
       </c>
       <c r="C544" t="n">
-        <v>601137</v>
+        <v>601136.952457838</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -18394,7 +18382,7 @@
         <v>2022</v>
       </c>
       <c r="C545" t="n">
-        <v>655326</v>
+        <v>655325.907489708</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -18427,7 +18415,7 @@
         <v>2023</v>
       </c>
       <c r="C546" t="n">
-        <v>764865</v>
+        <v>764864.848766634</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -18460,7 +18448,7 @@
         <v>2010</v>
       </c>
       <c r="C547" t="n">
-        <v>2287540</v>
+        <v>2287538.67680968</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -18493,7 +18481,7 @@
         <v>2011</v>
       </c>
       <c r="C548" t="n">
-        <v>2836030</v>
+        <v>2836030.42130108</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -18526,7 +18514,7 @@
         <v>2012</v>
       </c>
       <c r="C549" t="n">
-        <v>3850310</v>
+        <v>3850314.62650698</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -18559,7 +18547,7 @@
         <v>2013</v>
       </c>
       <c r="C550" t="n">
-        <v>5900280</v>
+        <v>5900276.79928739</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -18592,7 +18580,7 @@
         <v>2014</v>
       </c>
       <c r="C551" t="n">
-        <v>6291810</v>
+        <v>6291806.8091731</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -18625,7 +18613,7 @@
         <v>2015</v>
       </c>
       <c r="C552" t="n">
-        <v>6672100</v>
+        <v>6672097.98853804</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -18658,7 +18646,7 @@
         <v>2016</v>
       </c>
       <c r="C553" t="n">
-        <v>7716320</v>
+        <v>7716321.68306753</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -18691,7 +18679,7 @@
         <v>2017</v>
       </c>
       <c r="C554" t="n">
-        <v>8047010</v>
+        <v>8047007.93803804</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -18724,7 +18712,7 @@
         <v>2010</v>
       </c>
       <c r="C555" t="n">
-        <v>22880.8</v>
+        <v>22880.7754294793</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -18757,7 +18745,7 @@
         <v>2011</v>
       </c>
       <c r="C556" t="n">
-        <v>34952.5</v>
+        <v>34952.4573762064</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -18790,7 +18778,7 @@
         <v>2012</v>
       </c>
       <c r="C557" t="n">
-        <v>44234</v>
+        <v>44234.02156556</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -18823,7 +18811,7 @@
         <v>2013</v>
       </c>
       <c r="C558" t="n">
-        <v>74515.3</v>
+        <v>74515.2781158564</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -18856,7 +18844,7 @@
         <v>2014</v>
       </c>
       <c r="C559" t="n">
-        <v>85249.39999999999</v>
+        <v>85249.397111249</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -18889,7 +18877,7 @@
         <v>2015</v>
       </c>
       <c r="C560" t="n">
-        <v>91007.10000000001</v>
+        <v>91007.13040866749</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -18922,7 +18910,7 @@
         <v>2016</v>
       </c>
       <c r="C561" t="n">
-        <v>102048</v>
+        <v>102047.949269923</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -18955,7 +18943,7 @@
         <v>2017</v>
       </c>
       <c r="C562" t="n">
-        <v>108103</v>
+        <v>108102.876874941</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -18988,7 +18976,7 @@
         <v>2010</v>
       </c>
       <c r="C563" t="n">
-        <v>293826</v>
+        <v>293826.348452979</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -19021,7 +19009,7 @@
         <v>2011</v>
       </c>
       <c r="C564" t="n">
-        <v>320973</v>
+        <v>320972.710231073</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -19054,7 +19042,7 @@
         <v>2012</v>
       </c>
       <c r="C565" t="n">
-        <v>439210</v>
+        <v>439210.428235559</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -19087,7 +19075,7 @@
         <v>2013</v>
       </c>
       <c r="C566" t="n">
-        <v>158711</v>
+        <v>158710.89410249</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -19120,7 +19108,7 @@
         <v>2014</v>
       </c>
       <c r="C567" t="n">
-        <v>204840</v>
+        <v>204840.213125885</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -19153,7 +19141,7 @@
         <v>2015</v>
       </c>
       <c r="C568" t="n">
-        <v>235965</v>
+        <v>235965.131095485</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -19186,7 +19174,7 @@
         <v>2016</v>
       </c>
       <c r="C569" t="n">
-        <v>267973</v>
+        <v>267973.439878402</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -19219,7 +19207,7 @@
         <v>2017</v>
       </c>
       <c r="C570" t="n">
-        <v>269287</v>
+        <v>269287.158422063</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -19252,7 +19240,7 @@
         <v>2010</v>
       </c>
       <c r="C571" t="n">
-        <v>16545</v>
+        <v>16544.9584648793</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -19285,7 +19273,7 @@
         <v>2011</v>
       </c>
       <c r="C572" t="n">
-        <v>24153</v>
+        <v>24153.0430693391</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -19318,7 +19306,7 @@
         <v>2012</v>
       </c>
       <c r="C573" t="n">
-        <v>26571.4</v>
+        <v>26571.4156930263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -19351,7 +19339,7 @@
         <v>2013</v>
       </c>
       <c r="C574" t="n">
-        <v>12546</v>
+        <v>12545.9816762801</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -19384,7 +19372,7 @@
         <v>2014</v>
       </c>
       <c r="C575" t="n">
-        <v>13850.7</v>
+        <v>13850.7365704108</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -19417,7 +19405,7 @@
         <v>2015</v>
       </c>
       <c r="C576" t="n">
-        <v>15679.6</v>
+        <v>15679.5870122218</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -19450,7 +19438,7 @@
         <v>2016</v>
       </c>
       <c r="C577" t="n">
-        <v>17248.9</v>
+        <v>17248.9200803956</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -19483,7 +19471,7 @@
         <v>2017</v>
       </c>
       <c r="C578" t="n">
-        <v>17252.7</v>
+        <v>17252.6652034838</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -19516,7 +19504,7 @@
         <v>2013</v>
       </c>
       <c r="C579" t="n">
-        <v>21035.9</v>
+        <v>21035.9276432934</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -19549,7 +19537,7 @@
         <v>2014</v>
       </c>
       <c r="C580" t="n">
-        <v>25946.1</v>
+        <v>25946.073105079</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -19582,7 +19570,7 @@
         <v>2015</v>
       </c>
       <c r="C581" t="n">
-        <v>32786</v>
+        <v>32786.0410922882</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -19615,7 +19603,7 @@
         <v>2016</v>
       </c>
       <c r="C582" t="n">
-        <v>37694.4</v>
+        <v>37694.3724814843</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -19648,7 +19636,7 @@
         <v>2017</v>
       </c>
       <c r="C583" t="n">
-        <v>39006.9</v>
+        <v>39006.8807543701</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -19681,7 +19669,7 @@
         <v>2018</v>
       </c>
       <c r="C584" t="n">
-        <v>50639.4</v>
+        <v>50639.4309230881</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -19714,7 +19702,7 @@
         <v>2019</v>
       </c>
       <c r="C585" t="n">
-        <v>55889.3</v>
+        <v>55889.3063499707</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -19747,7 +19735,7 @@
         <v>2020</v>
       </c>
       <c r="C586" t="n">
-        <v>82780.8</v>
+        <v>82780.813573554</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -19780,7 +19768,7 @@
         <v>2021</v>
       </c>
       <c r="C587" t="n">
-        <v>137128</v>
+        <v>137127.709904652</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -19813,7 +19801,7 @@
         <v>2022</v>
       </c>
       <c r="C588" t="n">
-        <v>154247</v>
+        <v>154246.975133994</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -19846,7 +19834,7 @@
         <v>2023</v>
       </c>
       <c r="C589" t="n">
-        <v>190733</v>
+        <v>190732.62122009</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -19879,7 +19867,7 @@
         <v>2010</v>
       </c>
       <c r="C590" t="n">
-        <v>21534.2</v>
+        <v>21534.2423328554</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -19912,7 +19900,7 @@
         <v>2011</v>
       </c>
       <c r="C591" t="n">
-        <v>58672.7</v>
+        <v>58672.6829011186</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -19945,7 +19933,7 @@
         <v>2012</v>
       </c>
       <c r="C592" t="n">
-        <v>62207.2</v>
+        <v>62207.1575734089</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -19978,7 +19966,7 @@
         <v>2013</v>
       </c>
       <c r="C593" t="n">
-        <v>18192.8</v>
+        <v>18192.7646527642</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -20011,7 +19999,7 @@
         <v>2014</v>
       </c>
       <c r="C594" t="n">
-        <v>22786.3</v>
+        <v>22786.2597751802</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -20044,7 +20032,7 @@
         <v>2015</v>
       </c>
       <c r="C595" t="n">
-        <v>25413.9</v>
+        <v>25413.8954826625</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -20077,7 +20065,7 @@
         <v>2016</v>
       </c>
       <c r="C596" t="n">
-        <v>29326.9</v>
+        <v>29326.9203785741</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -20110,7 +20098,7 @@
         <v>2017</v>
       </c>
       <c r="C597" t="n">
-        <v>31743</v>
+        <v>31742.9666854771</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -20143,7 +20131,7 @@
         <v>2010</v>
       </c>
       <c r="C598" t="n">
-        <v>213260</v>
+        <v>213259.812723763</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -20176,7 +20164,7 @@
         <v>2011</v>
       </c>
       <c r="C599" t="n">
-        <v>222240</v>
+        <v>222239.648632766</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -20209,7 +20197,7 @@
         <v>2012</v>
       </c>
       <c r="C600" t="n">
-        <v>315143</v>
+        <v>315143.032392397</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -20242,7 +20230,7 @@
         <v>2013</v>
       </c>
       <c r="C601" t="n">
-        <v>39580.8</v>
+        <v>39580.7770748139</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -20275,7 +20263,7 @@
         <v>2014</v>
       </c>
       <c r="C602" t="n">
-        <v>47440.1</v>
+        <v>47440.125662705</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -20308,7 +20296,7 @@
         <v>2015</v>
       </c>
       <c r="C603" t="n">
-        <v>54084.5</v>
+        <v>54084.4969238677</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -20341,7 +20329,7 @@
         <v>2016</v>
       </c>
       <c r="C604" t="n">
-        <v>60463.9</v>
+        <v>60463.8788787578</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -20374,7 +20362,7 @@
         <v>2017</v>
       </c>
       <c r="C605" t="n">
-        <v>63631.8</v>
+        <v>63631.8136001468</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -20407,7 +20395,7 @@
         <v>2010</v>
       </c>
       <c r="C606" t="n">
-        <v>51821.6</v>
+        <v>51821.5681019186</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -20440,7 +20428,7 @@
         <v>2011</v>
       </c>
       <c r="C607" t="n">
-        <v>60790.1</v>
+        <v>60790.0999802812</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -20473,7 +20461,7 @@
         <v>2012</v>
       </c>
       <c r="C608" t="n">
-        <v>67845.7</v>
+        <v>67845.699722547</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -20506,7 +20494,7 @@
         <v>2013</v>
       </c>
       <c r="C609" t="n">
-        <v>55921.9</v>
+        <v>55921.8572280946</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -20539,7 +20527,7 @@
         <v>2014</v>
       </c>
       <c r="C610" t="n">
-        <v>65584.89999999999</v>
+        <v>65584.88846439539</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -20572,7 +20560,7 @@
         <v>2015</v>
       </c>
       <c r="C611" t="n">
-        <v>77671.89999999999</v>
+        <v>77671.9012673627</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -20605,7 +20593,7 @@
         <v>2016</v>
       </c>
       <c r="C612" t="n">
-        <v>94597.10000000001</v>
+        <v>94597.1447185929</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -20638,7 +20626,7 @@
         <v>2017</v>
       </c>
       <c r="C613" t="n">
-        <v>99917.10000000001</v>
+        <v>99917.0872910818</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -20671,7 +20659,7 @@
         <v>2018</v>
       </c>
       <c r="C614" t="n">
-        <v>122316</v>
+        <v>122315.691712077</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -20704,7 +20692,7 @@
         <v>2019</v>
       </c>
       <c r="C615" t="n">
-        <v>158392</v>
+        <v>158391.966359466</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -20737,7 +20725,7 @@
         <v>2020</v>
       </c>
       <c r="C616" t="n">
-        <v>248633</v>
+        <v>248632.646489591</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -20770,7 +20758,7 @@
         <v>2021</v>
       </c>
       <c r="C617" t="n">
-        <v>370689</v>
+        <v>370689.483859429</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -20803,7 +20791,7 @@
         <v>2022</v>
       </c>
       <c r="C618" t="n">
-        <v>401664</v>
+        <v>401663.555890902</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -20836,7 +20824,7 @@
         <v>2023</v>
       </c>
       <c r="C619" t="n">
-        <v>445866</v>
+        <v>445865.645516702</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -20869,7 +20857,7 @@
         <v>2010</v>
       </c>
       <c r="C620" t="n">
-        <v>45014.5</v>
+        <v>45014.4709951754</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -20902,7 +20890,7 @@
         <v>2011</v>
       </c>
       <c r="C621" t="n">
-        <v>57156.7</v>
+        <v>57156.7215736328</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -20935,7 +20923,7 @@
         <v>2012</v>
       </c>
       <c r="C622" t="n">
-        <v>66543.5</v>
+        <v>66543.5146019424</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -20968,7 +20956,7 @@
         <v>2013</v>
       </c>
       <c r="C623" t="n">
-        <v>35200.7</v>
+        <v>35200.6718952032</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -21001,7 +20989,7 @@
         <v>2014</v>
       </c>
       <c r="C624" t="n">
-        <v>38983.7</v>
+        <v>38983.6635629966</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -21034,7 +21022,7 @@
         <v>2015</v>
       </c>
       <c r="C625" t="n">
-        <v>42757.7</v>
+        <v>42757.7169127484</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -21067,7 +21055,7 @@
         <v>2016</v>
       </c>
       <c r="C626" t="n">
-        <v>47094.8</v>
+        <v>47094.8014555332</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -21100,7 +21088,7 @@
         <v>2017</v>
       </c>
       <c r="C627" t="n">
-        <v>47052.8</v>
+        <v>47052.8325520603</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -21133,7 +21121,7 @@
         <v>2010</v>
       </c>
       <c r="C628" t="n">
-        <v>7119.99</v>
+        <v>7119.98674193401</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -21166,7 +21154,7 @@
         <v>2011</v>
       </c>
       <c r="C629" t="n">
-        <v>11196.2</v>
+        <v>11196.1682195971</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -21199,7 +21187,7 @@
         <v>2012</v>
       </c>
       <c r="C630" t="n">
-        <v>14178.1</v>
+        <v>14178.1137111763</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -21232,7 +21220,7 @@
         <v>2013</v>
       </c>
       <c r="C631" t="n">
-        <v>20921.9</v>
+        <v>20921.9234465276</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -21265,7 +21253,7 @@
         <v>2014</v>
       </c>
       <c r="C632" t="n">
-        <v>27128.7</v>
+        <v>27128.6616723462</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -21298,7 +21286,7 @@
         <v>2015</v>
       </c>
       <c r="C633" t="n">
-        <v>35389.9</v>
+        <v>35389.8647558332</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -21331,7 +21319,7 @@
         <v>2016</v>
       </c>
       <c r="C634" t="n">
-        <v>42091.9</v>
+        <v>42091.8553024238</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -21364,7 +21352,7 @@
         <v>2017</v>
       </c>
       <c r="C635" t="n">
-        <v>43357.4</v>
+        <v>43357.4050628435</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -21397,7 +21385,7 @@
         <v>2010</v>
       </c>
       <c r="C636" t="n">
-        <v>25881.1</v>
+        <v>25881.1142755821</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -21430,7 +21418,7 @@
         <v>2011</v>
       </c>
       <c r="C637" t="n">
-        <v>34504</v>
+        <v>34504.0264067967</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -21463,7 +21451,7 @@
         <v>2012</v>
       </c>
       <c r="C638" t="n">
-        <v>41216</v>
+        <v>41216.0249191271</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -21496,7 +21484,7 @@
         <v>2013</v>
       </c>
       <c r="C639" t="n">
-        <v>57833.7</v>
+        <v>57833.7202800567</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -21529,7 +21517,7 @@
         <v>2014</v>
       </c>
       <c r="C640" t="n">
-        <v>73521.2</v>
+        <v>73521.2069013486</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -21562,7 +21550,7 @@
         <v>2015</v>
       </c>
       <c r="C641" t="n">
-        <v>101554</v>
+        <v>101553.801392325</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -21595,7 +21583,7 @@
         <v>2016</v>
       </c>
       <c r="C642" t="n">
-        <v>107846</v>
+        <v>107846.268169006</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -21628,7 +21616,7 @@
         <v>2017</v>
       </c>
       <c r="C643" t="n">
-        <v>111599</v>
+        <v>111599.290683536</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -21661,7 +21649,7 @@
         <v>2018</v>
       </c>
       <c r="C644" t="n">
-        <v>161851</v>
+        <v>161850.583412313</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -21694,7 +21682,7 @@
         <v>2019</v>
       </c>
       <c r="C645" t="n">
-        <v>190724</v>
+        <v>190723.91168433</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -21727,7 +21715,7 @@
         <v>2020</v>
       </c>
       <c r="C646" t="n">
-        <v>246304</v>
+        <v>246304.247032792</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -21760,7 +21748,7 @@
         <v>2021</v>
       </c>
       <c r="C647" t="n">
-        <v>310299</v>
+        <v>310298.573506388</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -21793,7 +21781,7 @@
         <v>2022</v>
       </c>
       <c r="C648" t="n">
-        <v>389768</v>
+        <v>389768.370567618</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -21826,7 +21814,7 @@
         <v>2023</v>
       </c>
       <c r="C649" t="n">
-        <v>489470</v>
+        <v>489470.406609565</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -21859,7 +21847,7 @@
         <v>2010</v>
       </c>
       <c r="C650" t="n">
-        <v>6416.96</v>
+        <v>6416.96131214025</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -21892,7 +21880,7 @@
         <v>2011</v>
       </c>
       <c r="C651" t="n">
-        <v>6462.08</v>
+        <v>6462.07896970681</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -21925,7 +21913,7 @@
         <v>2012</v>
       </c>
       <c r="C652" t="n">
-        <v>13023.5</v>
+        <v>13023.5194342166</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -21958,7 +21946,7 @@
         <v>2013</v>
       </c>
       <c r="C653" t="n">
-        <v>29177.3</v>
+        <v>29177.3044990647</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -21991,7 +21979,7 @@
         <v>2014</v>
       </c>
       <c r="C654" t="n">
-        <v>49361.2</v>
+        <v>49361.2302513422</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -22024,7 +22012,7 @@
         <v>2015</v>
       </c>
       <c r="C655" t="n">
-        <v>52020.4</v>
+        <v>52020.361997514</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -22057,7 +22045,7 @@
         <v>2016</v>
       </c>
       <c r="C656" t="n">
-        <v>57441.9</v>
+        <v>57441.9108151592</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -22090,7 +22078,7 @@
         <v>2017</v>
       </c>
       <c r="C657" t="n">
-        <v>66051.8</v>
+        <v>66051.7567354863</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -22123,7 +22111,7 @@
         <v>2018</v>
       </c>
       <c r="C658" t="n">
-        <v>84905.3</v>
+        <v>84905.25516373781</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -22156,7 +22144,7 @@
         <v>2019</v>
       </c>
       <c r="C659" t="n">
-        <v>90413</v>
+        <v>90412.9931029978</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -22189,7 +22177,7 @@
         <v>2020</v>
       </c>
       <c r="C660" t="n">
-        <v>136941</v>
+        <v>136941.279002065</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -22222,7 +22210,7 @@
         <v>2021</v>
       </c>
       <c r="C661" t="n">
-        <v>155015</v>
+        <v>155014.806843219</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -22255,7 +22243,7 @@
         <v>2022</v>
       </c>
       <c r="C662" t="n">
-        <v>159118</v>
+        <v>159117.620396839</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -22288,7 +22276,7 @@
         <v>2023</v>
       </c>
       <c r="C663" t="n">
-        <v>192198</v>
+        <v>192198.434034792</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -22321,7 +22309,7 @@
         <v>2010</v>
       </c>
       <c r="C664" t="n">
-        <v>9273.25</v>
+        <v>9273.25328537454</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -22354,7 +22342,7 @@
         <v>2011</v>
       </c>
       <c r="C665" t="n">
-        <v>9262.5</v>
+        <v>9262.502850535249</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -22387,7 +22375,7 @@
         <v>2012</v>
       </c>
       <c r="C666" t="n">
-        <v>9250.91</v>
+        <v>9250.91459167111</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -22420,7 +22408,7 @@
         <v>2013</v>
       </c>
       <c r="C667" t="n">
-        <v>9241.42</v>
+        <v>9241.423312266579</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -22453,7 +22441,7 @@
         <v>2014</v>
       </c>
       <c r="C668" t="n">
-        <v>12003.2</v>
+        <v>12003.1836136231</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -22486,7 +22474,7 @@
         <v>2015</v>
       </c>
       <c r="C669" t="n">
-        <v>32261.6</v>
+        <v>32261.6293850611</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -22519,7 +22507,7 @@
         <v>2016</v>
       </c>
       <c r="C670" t="n">
-        <v>42394.7</v>
+        <v>42394.6968442081</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -22552,7 +22540,7 @@
         <v>2017</v>
       </c>
       <c r="C671" t="n">
-        <v>63564.6</v>
+        <v>63564.582298508</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -22585,7 +22573,7 @@
         <v>2018</v>
       </c>
       <c r="C672" t="n">
-        <v>77632.39999999999</v>
+        <v>77632.3698861265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -22618,7 +22606,7 @@
         <v>2019</v>
       </c>
       <c r="C673" t="n">
-        <v>58435.9</v>
+        <v>58435.8567254477</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -22651,7 +22639,7 @@
         <v>2020</v>
       </c>
       <c r="C674" t="n">
-        <v>58192.6</v>
+        <v>58192.5945697031</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -22684,7 +22672,7 @@
         <v>2021</v>
       </c>
       <c r="C675" t="n">
-        <v>64708.9</v>
+        <v>64708.9095806006</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -22717,7 +22705,7 @@
         <v>2022</v>
       </c>
       <c r="C676" t="n">
-        <v>86134.8</v>
+        <v>86134.8495221349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -22750,7 +22738,7 @@
         <v>2023</v>
       </c>
       <c r="C677" t="n">
-        <v>116280</v>
+        <v>116279.739872111</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -22783,7 +22771,7 @@
         <v>2010</v>
       </c>
       <c r="C678" t="n">
-        <v>14393.3</v>
+        <v>14393.3392424221</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -22816,7 +22804,7 @@
         <v>2011</v>
       </c>
       <c r="C679" t="n">
-        <v>27847.7</v>
+        <v>27847.6576410466</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -22849,7 +22837,7 @@
         <v>2012</v>
       </c>
       <c r="C680" t="n">
-        <v>27373.6</v>
+        <v>27373.5615193422</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -22882,7 +22870,7 @@
         <v>2013</v>
       </c>
       <c r="C681" t="n">
-        <v>37238.6</v>
+        <v>37238.623996846</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -22915,7 +22903,7 @@
         <v>2014</v>
       </c>
       <c r="C682" t="n">
-        <v>38543.9</v>
+        <v>38543.9185213343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -22948,7 +22936,7 @@
         <v>2015</v>
       </c>
       <c r="C683" t="n">
-        <v>68457.10000000001</v>
+        <v>68457.0576127417</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -22981,7 +22969,7 @@
         <v>2016</v>
       </c>
       <c r="C684" t="n">
-        <v>59130.2</v>
+        <v>59130.1736276005</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -23014,7 +23002,7 @@
         <v>2017</v>
       </c>
       <c r="C685" t="n">
-        <v>110260</v>
+        <v>110259.718261869</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -23047,7 +23035,7 @@
         <v>2018</v>
       </c>
       <c r="C686" t="n">
-        <v>171833</v>
+        <v>171832.808282477</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -23080,7 +23068,7 @@
         <v>2019</v>
       </c>
       <c r="C687" t="n">
-        <v>342867</v>
+        <v>342866.871615806</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -23113,7 +23101,7 @@
         <v>2020</v>
       </c>
       <c r="C688" t="n">
-        <v>267194</v>
+        <v>267194.151891391</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -23146,7 +23134,7 @@
         <v>2021</v>
       </c>
       <c r="C689" t="n">
-        <v>211603</v>
+        <v>211602.656749999</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -23179,7 +23167,7 @@
         <v>2022</v>
       </c>
       <c r="C690" t="n">
-        <v>194924</v>
+        <v>194923.977582729</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -23212,7 +23200,7 @@
         <v>2023</v>
       </c>
       <c r="C691" t="n">
-        <v>194938</v>
+        <v>194938.432598315</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -23245,7 +23233,7 @@
         <v>2010</v>
       </c>
       <c r="C692" t="n">
-        <v>54950.4</v>
+        <v>54950.3531912872</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -23278,7 +23266,7 @@
         <v>2011</v>
       </c>
       <c r="C693" t="n">
-        <v>64673.9</v>
+        <v>64673.9355731998</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -23311,7 +23299,7 @@
         <v>2012</v>
       </c>
       <c r="C694" t="n">
-        <v>75664.10000000001</v>
+        <v>75664.10696197741</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -23344,7 +23332,7 @@
         <v>2013</v>
       </c>
       <c r="C695" t="n">
-        <v>106490</v>
+        <v>106490.168440852</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -23377,7 +23365,7 @@
         <v>2014</v>
       </c>
       <c r="C696" t="n">
-        <v>47664.6</v>
+        <v>47664.6151630566</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -23410,7 +23398,7 @@
         <v>2015</v>
       </c>
       <c r="C697" t="n">
-        <v>49615.4</v>
+        <v>49615.3528068196</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -23443,7 +23431,7 @@
         <v>2016</v>
       </c>
       <c r="C698" t="n">
-        <v>53609.2</v>
+        <v>53609.2098509594</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -23476,7 +23464,7 @@
         <v>2017</v>
       </c>
       <c r="C699" t="n">
-        <v>52344.1</v>
+        <v>52344.1314612332</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -23509,7 +23497,7 @@
         <v>2010</v>
       </c>
       <c r="C700" t="n">
-        <v>9031.379999999999</v>
+        <v>9031.380925760561</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -23542,7 +23530,7 @@
         <v>2011</v>
       </c>
       <c r="C701" t="n">
-        <v>13396.5</v>
+        <v>13396.4985442111</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -23575,7 +23563,7 @@
         <v>2012</v>
       </c>
       <c r="C702" t="n">
-        <v>18497.1</v>
+        <v>18497.0548581926</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -23608,7 +23596,7 @@
         <v>2013</v>
       </c>
       <c r="C703" t="n">
-        <v>20610.5</v>
+        <v>20610.477440232</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -23641,7 +23629,7 @@
         <v>2014</v>
       </c>
       <c r="C704" t="n">
-        <v>25888.2</v>
+        <v>25888.2471989501</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -23674,7 +23662,7 @@
         <v>2015</v>
       </c>
       <c r="C705" t="n">
-        <v>34621.9</v>
+        <v>34621.9143801389</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -23707,7 +23695,7 @@
         <v>2016</v>
       </c>
       <c r="C706" t="n">
-        <v>33691.4</v>
+        <v>33691.3658805964</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -23740,7 +23728,7 @@
         <v>2017</v>
       </c>
       <c r="C707" t="n">
-        <v>45713.6</v>
+        <v>45713.5722923131</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -23773,7 +23761,7 @@
         <v>2018</v>
       </c>
       <c r="C708" t="n">
-        <v>51674.1</v>
+        <v>51674.1218545693</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -23806,7 +23794,7 @@
         <v>2019</v>
       </c>
       <c r="C709" t="n">
-        <v>59155.4</v>
+        <v>59155.3597807268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -23839,7 +23827,7 @@
         <v>2020</v>
       </c>
       <c r="C710" t="n">
-        <v>79872.39999999999</v>
+        <v>79872.3607627219</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -23872,7 +23860,7 @@
         <v>2021</v>
       </c>
       <c r="C711" t="n">
-        <v>78636.3</v>
+        <v>78636.3051669597</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -23905,7 +23893,7 @@
         <v>2022</v>
       </c>
       <c r="C712" t="n">
-        <v>120266</v>
+        <v>120265.886625238</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -23938,7 +23926,7 @@
         <v>2023</v>
       </c>
       <c r="C713" t="n">
-        <v>263967</v>
+        <v>263966.687366159</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -23971,7 +23959,7 @@
         <v>2010</v>
       </c>
       <c r="C714" t="n">
-        <v>74270.89999999999</v>
+        <v>74270.8931172146</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -24004,7 +23992,7 @@
         <v>2011</v>
       </c>
       <c r="C715" t="n">
-        <v>87395.7</v>
+        <v>87395.6774639752</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -24037,7 +24025,7 @@
         <v>2012</v>
       </c>
       <c r="C716" t="n">
-        <v>95523.2</v>
+        <v>95523.2206084709</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -24070,7 +24058,7 @@
         <v>2013</v>
       </c>
       <c r="C717" t="n">
-        <v>100323</v>
+        <v>100322.546695446</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -24103,7 +24091,7 @@
         <v>2014</v>
       </c>
       <c r="C718" t="n">
-        <v>109143</v>
+        <v>109143.497258188</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -24136,7 +24124,7 @@
         <v>2015</v>
       </c>
       <c r="C719" t="n">
-        <v>117831</v>
+        <v>117831.023539325</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -24169,7 +24157,7 @@
         <v>2016</v>
       </c>
       <c r="C720" t="n">
-        <v>131570</v>
+        <v>131570.175807084</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -24202,7 +24190,7 @@
         <v>2017</v>
       </c>
       <c r="C721" t="n">
-        <v>135339</v>
+        <v>135339.025493815</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -24235,7 +24223,7 @@
         <v>2010</v>
       </c>
       <c r="C722" t="n">
-        <v>22199.7</v>
+        <v>22199.6975476096</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -24268,7 +24256,7 @@
         <v>2011</v>
       </c>
       <c r="C723" t="n">
-        <v>53250.5</v>
+        <v>53250.4781979846</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -24301,7 +24289,7 @@
         <v>2012</v>
       </c>
       <c r="C724" t="n">
-        <v>78844.3</v>
+        <v>78844.2966663199</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -24334,7 +24322,7 @@
         <v>2013</v>
       </c>
       <c r="C725" t="n">
-        <v>93717.60000000001</v>
+        <v>93717.5572938103</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -24367,7 +24355,7 @@
         <v>2014</v>
       </c>
       <c r="C726" t="n">
-        <v>140060</v>
+        <v>140060.44312417</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -24400,7 +24388,7 @@
         <v>2015</v>
       </c>
       <c r="C727" t="n">
-        <v>136030</v>
+        <v>136030.347733504</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -24433,7 +24421,7 @@
         <v>2016</v>
       </c>
       <c r="C728" t="n">
-        <v>163445</v>
+        <v>163444.552091145</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -24466,7 +24454,7 @@
         <v>2017</v>
       </c>
       <c r="C729" t="n">
-        <v>189318</v>
+        <v>189317.742156235</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -24499,7 +24487,7 @@
         <v>2018</v>
       </c>
       <c r="C730" t="n">
-        <v>197330</v>
+        <v>197330.206379516</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -24532,7 +24520,7 @@
         <v>2019</v>
       </c>
       <c r="C731" t="n">
-        <v>198584</v>
+        <v>198584.052682143</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -24565,7 +24553,7 @@
         <v>2020</v>
       </c>
       <c r="C732" t="n">
-        <v>242940</v>
+        <v>242940.288036754</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -24598,7 +24586,7 @@
         <v>2021</v>
       </c>
       <c r="C733" t="n">
-        <v>235247</v>
+        <v>235246.869715666</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -24631,7 +24619,7 @@
         <v>2022</v>
       </c>
       <c r="C734" t="n">
-        <v>279756</v>
+        <v>279756.233103327</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -24664,7 +24652,7 @@
         <v>2023</v>
       </c>
       <c r="C735" t="n">
-        <v>371015</v>
+        <v>371014.739453513</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -24697,7 +24685,7 @@
         <v>2010</v>
       </c>
       <c r="C736" t="n">
-        <v>67647.7</v>
+        <v>67647.7034397478</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -24730,7 +24718,7 @@
         <v>2011</v>
       </c>
       <c r="C737" t="n">
-        <v>71393.60000000001</v>
+        <v>71393.562880659</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -24763,7 +24751,7 @@
         <v>2012</v>
       </c>
       <c r="C738" t="n">
-        <v>90283.7</v>
+        <v>90283.6995270093</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -24796,7 +24784,7 @@
         <v>2013</v>
       </c>
       <c r="C739" t="n">
-        <v>107238</v>
+        <v>107237.757966868</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -24829,7 +24817,7 @@
         <v>2014</v>
       </c>
       <c r="C740" t="n">
-        <v>134075</v>
+        <v>134074.905845208</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -24862,7 +24850,7 @@
         <v>2015</v>
       </c>
       <c r="C741" t="n">
-        <v>151927</v>
+        <v>151926.51251134</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -24895,7 +24883,7 @@
         <v>2016</v>
       </c>
       <c r="C742" t="n">
-        <v>207593</v>
+        <v>207592.522146949</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -24928,7 +24916,7 @@
         <v>2017</v>
       </c>
       <c r="C743" t="n">
-        <v>179619</v>
+        <v>179618.818904926</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -24961,7 +24949,7 @@
         <v>2018</v>
       </c>
       <c r="C744" t="n">
-        <v>457456</v>
+        <v>457456.104461833</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -24994,7 +24982,7 @@
         <v>2019</v>
       </c>
       <c r="C745" t="n">
-        <v>486526</v>
+        <v>486526.285221731</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -25027,7 +25015,7 @@
         <v>2020</v>
       </c>
       <c r="C746" t="n">
-        <v>539773</v>
+        <v>539773.24536716</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -25060,7 +25048,7 @@
         <v>2021</v>
       </c>
       <c r="C747" t="n">
-        <v>576358</v>
+        <v>576357.584312973</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -25093,7 +25081,7 @@
         <v>2022</v>
       </c>
       <c r="C748" t="n">
-        <v>771871</v>
+        <v>771870.751870252</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -25126,7 +25114,7 @@
         <v>2023</v>
       </c>
       <c r="C749" t="n">
-        <v>649095</v>
+        <v>649094.895998259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -25159,7 +25147,7 @@
         <v>2010</v>
       </c>
       <c r="C750" t="n">
-        <v>67863.60000000001</v>
+        <v>67863.6404636462</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -25192,7 +25180,7 @@
         <v>2011</v>
       </c>
       <c r="C751" t="n">
-        <v>70389.2</v>
+        <v>70389.16220512619</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -25225,7 +25213,7 @@
         <v>2012</v>
       </c>
       <c r="C752" t="n">
-        <v>91656.8</v>
+        <v>91656.7750758122</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -25258,7 +25246,7 @@
         <v>2013</v>
       </c>
       <c r="C753" t="n">
-        <v>84098.5</v>
+        <v>84098.5101595406</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -25291,7 +25279,7 @@
         <v>2014</v>
       </c>
       <c r="C754" t="n">
-        <v>45242.7</v>
+        <v>45242.695294754</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -25324,7 +25312,7 @@
         <v>2015</v>
       </c>
       <c r="C755" t="n">
-        <v>54884.7</v>
+        <v>54884.6915368178</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -25357,7 +25345,7 @@
         <v>2016</v>
       </c>
       <c r="C756" t="n">
-        <v>59386.1</v>
+        <v>59386.066499138</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -25390,7 +25378,7 @@
         <v>2017</v>
       </c>
       <c r="C757" t="n">
-        <v>279451</v>
+        <v>279450.663912583</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -25423,7 +25411,7 @@
         <v>2018</v>
       </c>
       <c r="C758" t="n">
-        <v>313273</v>
+        <v>313273.424916256</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -25456,7 +25444,7 @@
         <v>2019</v>
       </c>
       <c r="C759" t="n">
-        <v>1128250</v>
+        <v>1128249.94139785</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -25489,7 +25477,7 @@
         <v>2020</v>
       </c>
       <c r="C760" t="n">
-        <v>1378790</v>
+        <v>1378788.9404157</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -25522,7 +25510,7 @@
         <v>2021</v>
       </c>
       <c r="C761" t="n">
-        <v>1558160</v>
+        <v>1558156.27856987</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -25555,7 +25543,7 @@
         <v>2022</v>
       </c>
       <c r="C762" t="n">
-        <v>2132350</v>
+        <v>2132353.68309265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -25588,7 +25576,7 @@
         <v>2023</v>
       </c>
       <c r="C763" t="n">
-        <v>2174860</v>
+        <v>2174862.03991292</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -25621,7 +25609,7 @@
         <v>2010</v>
       </c>
       <c r="C764" t="n">
-        <v>40387.3</v>
+        <v>40387.3290122382</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -25654,7 +25642,7 @@
         <v>2011</v>
       </c>
       <c r="C765" t="n">
-        <v>48914.4</v>
+        <v>48914.3779646115</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -25687,7 +25675,7 @@
         <v>2012</v>
       </c>
       <c r="C766" t="n">
-        <v>55321.7</v>
+        <v>55321.7016245239</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -25720,7 +25708,7 @@
         <v>2013</v>
       </c>
       <c r="C767" t="n">
-        <v>34451.1</v>
+        <v>34451.0628495079</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -25753,7 +25741,7 @@
         <v>2014</v>
       </c>
       <c r="C768" t="n">
-        <v>37068.2</v>
+        <v>37068.1622528757</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -25786,7 +25774,7 @@
         <v>2015</v>
       </c>
       <c r="C769" t="n">
-        <v>42425</v>
+        <v>42425.0070851873</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -25819,7 +25807,7 @@
         <v>2016</v>
       </c>
       <c r="C770" t="n">
-        <v>50247.5</v>
+        <v>50247.497013161</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -25852,7 +25840,7 @@
         <v>2017</v>
       </c>
       <c r="C771" t="n">
-        <v>53468.4</v>
+        <v>53468.3695118329</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -25885,7 +25873,7 @@
         <v>2010</v>
       </c>
       <c r="C772" t="n">
-        <v>92227.2</v>
+        <v>92227.1622345065</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -25918,7 +25906,7 @@
         <v>2011</v>
       </c>
       <c r="C773" t="n">
-        <v>101664</v>
+        <v>101663.737129516</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -25951,7 +25939,7 @@
         <v>2012</v>
       </c>
       <c r="C774" t="n">
-        <v>115103</v>
+        <v>115102.754849178</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -25984,7 +25972,7 @@
         <v>2013</v>
       </c>
       <c r="C775" t="n">
-        <v>57398</v>
+        <v>57398.0132558221</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -26017,7 +26005,7 @@
         <v>2014</v>
       </c>
       <c r="C776" t="n">
-        <v>64603.4</v>
+        <v>64603.350142402</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -26050,7 +26038,7 @@
         <v>2015</v>
       </c>
       <c r="C777" t="n">
-        <v>72144.3</v>
+        <v>72144.3044555333</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -26083,7 +26071,7 @@
         <v>2016</v>
       </c>
       <c r="C778" t="n">
-        <v>81015.3</v>
+        <v>81015.25225516981</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -26116,7 +26104,7 @@
         <v>2017</v>
       </c>
       <c r="C779" t="n">
-        <v>86639</v>
+        <v>86638.9926628606</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -26149,7 +26137,7 @@
         <v>2010</v>
       </c>
       <c r="C780" t="n">
-        <v>31696.4</v>
+        <v>31696.4099706955</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -26182,7 +26170,7 @@
         <v>2011</v>
       </c>
       <c r="C781" t="n">
-        <v>42052.5</v>
+        <v>42052.4739664969</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -26215,7 +26203,7 @@
         <v>2012</v>
       </c>
       <c r="C782" t="n">
-        <v>48540.6</v>
+        <v>48540.5707585007</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -26248,7 +26236,7 @@
         <v>2013</v>
       </c>
       <c r="C783" t="n">
-        <v>17873.9</v>
+        <v>17873.9317666968</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -26281,7 +26269,7 @@
         <v>2014</v>
       </c>
       <c r="C784" t="n">
-        <v>19665.9</v>
+        <v>19665.9189285073</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -26314,7 +26302,7 @@
         <v>2015</v>
       </c>
       <c r="C785" t="n">
-        <v>22594.1</v>
+        <v>22594.1204423896</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -26347,7 +26335,7 @@
         <v>2016</v>
       </c>
       <c r="C786" t="n">
-        <v>26827.1</v>
+        <v>26827.0672145525</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -26380,7 +26368,7 @@
         <v>2017</v>
       </c>
       <c r="C787" t="n">
-        <v>26732.7</v>
+        <v>26732.6510913981</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -26413,7 +26401,7 @@
         <v>2010</v>
       </c>
       <c r="C788" t="n">
-        <v>23312.3</v>
+        <v>23312.3158413203</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -26446,7 +26434,7 @@
         <v>2011</v>
       </c>
       <c r="C789" t="n">
-        <v>24620.1</v>
+        <v>24620.1390748325</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -26479,7 +26467,7 @@
         <v>2012</v>
       </c>
       <c r="C790" t="n">
-        <v>26041.7</v>
+        <v>26041.7243692694</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -26512,7 +26500,7 @@
         <v>2013</v>
       </c>
       <c r="C791" t="n">
-        <v>28452.4</v>
+        <v>28452.4196732379</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -26545,7 +26533,7 @@
         <v>2014</v>
       </c>
       <c r="C792" t="n">
-        <v>35762.2</v>
+        <v>35762.1992556118</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -26578,7 +26566,7 @@
         <v>2015</v>
       </c>
       <c r="C793" t="n">
-        <v>106693</v>
+        <v>106693.030726999</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -26611,7 +26599,7 @@
         <v>2016</v>
       </c>
       <c r="C794" t="n">
-        <v>121957</v>
+        <v>121956.559864841</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -26644,7 +26632,7 @@
         <v>2017</v>
       </c>
       <c r="C795" t="n">
-        <v>122342</v>
+        <v>122341.675588924</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -26677,7 +26665,7 @@
         <v>2010</v>
       </c>
       <c r="C796" t="n">
-        <v>71415.5</v>
+        <v>71415.54446605381</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -26710,7 +26698,7 @@
         <v>2011</v>
       </c>
       <c r="C797" t="n">
-        <v>79600.60000000001</v>
+        <v>79600.5863243795</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -26743,7 +26731,7 @@
         <v>2012</v>
       </c>
       <c r="C798" t="n">
-        <v>85362.60000000001</v>
+        <v>85362.6050198439</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -26776,7 +26764,7 @@
         <v>2013</v>
       </c>
       <c r="C799" t="n">
-        <v>36969.4</v>
+        <v>36969.4157153761</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -26809,7 +26797,7 @@
         <v>2014</v>
       </c>
       <c r="C800" t="n">
-        <v>39682</v>
+        <v>39682.0458247127</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -26842,7 +26830,7 @@
         <v>2015</v>
       </c>
       <c r="C801" t="n">
-        <v>47394.6</v>
+        <v>47394.6176121862</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -26875,7 +26863,7 @@
         <v>2016</v>
       </c>
       <c r="C802" t="n">
-        <v>52331.4</v>
+        <v>52331.4360730197</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -26908,7 +26896,7 @@
         <v>2017</v>
       </c>
       <c r="C803" t="n">
-        <v>54228</v>
+        <v>54228.0254735793</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -26941,7 +26929,7 @@
         <v>2010</v>
       </c>
       <c r="C804" t="n">
-        <v>67912.7</v>
+        <v>67912.7492108966</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -26974,7 +26962,7 @@
         <v>2011</v>
       </c>
       <c r="C805" t="n">
-        <v>82208.5</v>
+        <v>82208.4805685693</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -27007,7 +26995,7 @@
         <v>2012</v>
       </c>
       <c r="C806" t="n">
-        <v>97440.7</v>
+        <v>97440.7099500903</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -27040,7 +27028,7 @@
         <v>2013</v>
       </c>
       <c r="C807" t="n">
-        <v>51230.4</v>
+        <v>51230.3653437217</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -27073,7 +27061,7 @@
         <v>2014</v>
       </c>
       <c r="C808" t="n">
-        <v>64536.4</v>
+        <v>64536.3791061149</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -27106,7 +27094,7 @@
         <v>2015</v>
       </c>
       <c r="C809" t="n">
-        <v>72851.10000000001</v>
+        <v>72851.0779879194</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -27139,7 +27127,7 @@
         <v>2016</v>
       </c>
       <c r="C810" t="n">
-        <v>79880</v>
+        <v>79880.0447315936</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -27172,7 +27160,7 @@
         <v>2017</v>
       </c>
       <c r="C811" t="n">
-        <v>84057.39999999999</v>
+        <v>84057.4207271226</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -27205,7 +27193,7 @@
         <v>2010</v>
       </c>
       <c r="C812" t="n">
-        <v>31651.7</v>
+        <v>31651.7132521562</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -27238,7 +27226,7 @@
         <v>2011</v>
       </c>
       <c r="C813" t="n">
-        <v>52285.6</v>
+        <v>52285.6006406754</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -27271,7 +27259,7 @@
         <v>2012</v>
       </c>
       <c r="C814" t="n">
-        <v>65743</v>
+        <v>65743.0104167471</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -27304,7 +27292,7 @@
         <v>2013</v>
       </c>
       <c r="C815" t="n">
-        <v>73105.39999999999</v>
+        <v>73105.4227213913</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -27337,7 +27325,7 @@
         <v>2014</v>
       </c>
       <c r="C816" t="n">
-        <v>79880.60000000001</v>
+        <v>79880.5507201072</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -27370,7 +27358,7 @@
         <v>2015</v>
       </c>
       <c r="C817" t="n">
-        <v>76441.10000000001</v>
+        <v>76441.0715099638</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -27403,7 +27391,7 @@
         <v>2016</v>
       </c>
       <c r="C818" t="n">
-        <v>70894.60000000001</v>
+        <v>70894.6147800483</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -27436,7 +27424,7 @@
         <v>2017</v>
       </c>
       <c r="C819" t="n">
-        <v>88681.10000000001</v>
+        <v>88681.1099411269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -27469,7 +27457,7 @@
         <v>2018</v>
       </c>
       <c r="C820" t="n">
-        <v>114171</v>
+        <v>114171.220402933</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -27502,7 +27490,7 @@
         <v>2019</v>
       </c>
       <c r="C821" t="n">
-        <v>137573</v>
+        <v>137573.182918832</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -27535,7 +27523,7 @@
         <v>2020</v>
       </c>
       <c r="C822" t="n">
-        <v>200124</v>
+        <v>200124.134597463</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -27568,7 +27556,7 @@
         <v>2021</v>
       </c>
       <c r="C823" t="n">
-        <v>230174</v>
+        <v>230173.625014952</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -27601,7 +27589,7 @@
         <v>2022</v>
       </c>
       <c r="C824" t="n">
-        <v>253841</v>
+        <v>253840.569811514</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -27634,7 +27622,7 @@
         <v>2023</v>
       </c>
       <c r="C825" t="n">
-        <v>312445</v>
+        <v>312445.143601208</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -27667,7 +27655,7 @@
         <v>2010</v>
       </c>
       <c r="C826" t="n">
-        <v>60937.5</v>
+        <v>60937.490328372</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -27700,7 +27688,7 @@
         <v>2011</v>
       </c>
       <c r="C827" t="n">
-        <v>73185.2</v>
+        <v>73185.1788728776</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -27733,7 +27721,7 @@
         <v>2012</v>
       </c>
       <c r="C828" t="n">
-        <v>72386.8</v>
+        <v>72386.76572375921</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -27766,7 +27754,7 @@
         <v>2013</v>
       </c>
       <c r="C829" t="n">
-        <v>38975.5</v>
+        <v>38975.4652039988</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -27799,7 +27787,7 @@
         <v>2014</v>
       </c>
       <c r="C830" t="n">
-        <v>42216.4</v>
+        <v>42216.3993895578</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -27832,7 +27820,7 @@
         <v>2015</v>
       </c>
       <c r="C831" t="n">
-        <v>50932.4</v>
+        <v>50932.3874156942</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -27865,7 +27853,7 @@
         <v>2016</v>
       </c>
       <c r="C832" t="n">
-        <v>54657</v>
+        <v>54656.9665203088</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -27898,7 +27886,7 @@
         <v>2017</v>
       </c>
       <c r="C833" t="n">
-        <v>60581.8</v>
+        <v>60581.8148961429</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -27931,7 +27919,7 @@
         <v>2010</v>
       </c>
       <c r="C834" t="n">
-        <v>152877</v>
+        <v>152876.81441466</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -27964,7 +27952,7 @@
         <v>2011</v>
       </c>
       <c r="C835" t="n">
-        <v>162282</v>
+        <v>162282.490555629</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -27997,7 +27985,7 @@
         <v>2012</v>
       </c>
       <c r="C836" t="n">
-        <v>190992</v>
+        <v>190992.198573766</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -28030,7 +28018,7 @@
         <v>2013</v>
       </c>
       <c r="C837" t="n">
-        <v>87820.3</v>
+        <v>87820.31592716811</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -28063,7 +28051,7 @@
         <v>2014</v>
       </c>
       <c r="C838" t="n">
-        <v>99289.5</v>
+        <v>99289.504060084</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -28096,7 +28084,7 @@
         <v>2015</v>
       </c>
       <c r="C839" t="n">
-        <v>108338</v>
+        <v>108337.905438333</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -28129,7 +28117,7 @@
         <v>2016</v>
       </c>
       <c r="C840" t="n">
-        <v>115719</v>
+        <v>115718.954758977</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -28162,7 +28150,7 @@
         <v>2017</v>
       </c>
       <c r="C841" t="n">
-        <v>117739</v>
+        <v>117738.525448019</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -28195,7 +28183,7 @@
         <v>2010</v>
       </c>
       <c r="C842" t="n">
-        <v>22612.4</v>
+        <v>22612.3654925152</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -28228,7 +28216,7 @@
         <v>2011</v>
       </c>
       <c r="C843" t="n">
-        <v>25061.8</v>
+        <v>25061.7723153967</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -28261,7 +28249,7 @@
         <v>2012</v>
       </c>
       <c r="C844" t="n">
-        <v>37905.1</v>
+        <v>37905.0682247929</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -28294,7 +28282,7 @@
         <v>2013</v>
       </c>
       <c r="C845" t="n">
-        <v>40964.8</v>
+        <v>40964.8081414244</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -28327,7 +28315,7 @@
         <v>2014</v>
       </c>
       <c r="C846" t="n">
-        <v>51845.6</v>
+        <v>51845.5618509844</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -28360,7 +28348,7 @@
         <v>2015</v>
       </c>
       <c r="C847" t="n">
-        <v>57980</v>
+        <v>57980.025736778</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -28393,7 +28381,7 @@
         <v>2016</v>
       </c>
       <c r="C848" t="n">
-        <v>74672.7</v>
+        <v>74672.72633174949</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -28426,7 +28414,7 @@
         <v>2017</v>
       </c>
       <c r="C849" t="n">
-        <v>129078</v>
+        <v>129077.663969402</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -28459,7 +28447,7 @@
         <v>2018</v>
       </c>
       <c r="C850" t="n">
-        <v>142194</v>
+        <v>142193.920665093</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -28492,7 +28480,7 @@
         <v>2019</v>
       </c>
       <c r="C851" t="n">
-        <v>177535</v>
+        <v>177534.50914173</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -28525,7 +28513,7 @@
         <v>2020</v>
       </c>
       <c r="C852" t="n">
-        <v>229171</v>
+        <v>229170.633024854</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -28558,7 +28546,7 @@
         <v>2021</v>
       </c>
       <c r="C853" t="n">
-        <v>271996</v>
+        <v>271995.87706572</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -28591,7 +28579,7 @@
         <v>2022</v>
       </c>
       <c r="C854" t="n">
-        <v>266294</v>
+        <v>266293.653941594</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -28624,7 +28612,7 @@
         <v>2010</v>
       </c>
       <c r="C855" t="n">
-        <v>61926.9</v>
+        <v>61926.8869071221</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -28657,7 +28645,7 @@
         <v>2011</v>
       </c>
       <c r="C856" t="n">
-        <v>63957.9</v>
+        <v>63957.9190382181</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -28690,7 +28678,7 @@
         <v>2012</v>
       </c>
       <c r="C857" t="n">
-        <v>73976</v>
+        <v>73976.00138249771</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -28723,7 +28711,7 @@
         <v>2013</v>
       </c>
       <c r="C858" t="n">
-        <v>22562</v>
+        <v>22562.0145241151</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -28756,7 +28744,7 @@
         <v>2014</v>
       </c>
       <c r="C859" t="n">
-        <v>26664.6</v>
+        <v>26664.604088677</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -28789,7 +28777,7 @@
         <v>2015</v>
       </c>
       <c r="C860" t="n">
-        <v>28393.3</v>
+        <v>28393.3296443505</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -28822,7 +28810,7 @@
         <v>2016</v>
       </c>
       <c r="C861" t="n">
-        <v>32355.7</v>
+        <v>32355.6994001854</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -28855,7 +28843,7 @@
         <v>2017</v>
       </c>
       <c r="C862" t="n">
-        <v>34127.4</v>
+        <v>34127.3539681706</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -28888,7 +28876,7 @@
         <v>2010</v>
       </c>
       <c r="C863" t="n">
-        <v>68574</v>
+        <v>68573.970225906</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -28921,7 +28909,7 @@
         <v>2011</v>
       </c>
       <c r="C864" t="n">
-        <v>82135.5</v>
+        <v>82135.482307454</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -28954,7 +28942,7 @@
         <v>2012</v>
       </c>
       <c r="C865" t="n">
-        <v>83964</v>
+        <v>83964.00087586429</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -28987,7 +28975,7 @@
         <v>2013</v>
       </c>
       <c r="C866" t="n">
-        <v>59413.4</v>
+        <v>59413.4303708436</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -29020,7 +29008,7 @@
         <v>2014</v>
       </c>
       <c r="C867" t="n">
-        <v>66851</v>
+        <v>66851.03889067459</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -29053,7 +29041,7 @@
         <v>2015</v>
       </c>
       <c r="C868" t="n">
-        <v>75133.7</v>
+        <v>75133.7433390206</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -29086,7 +29074,7 @@
         <v>2016</v>
       </c>
       <c r="C869" t="n">
-        <v>75582.5</v>
+        <v>75582.4572164462</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -29119,7 +29107,7 @@
         <v>2017</v>
       </c>
       <c r="C870" t="n">
-        <v>77852.7</v>
+        <v>77852.6840306915</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -29152,7 +29140,7 @@
         <v>2010</v>
       </c>
       <c r="C871" t="n">
-        <v>48738.1</v>
+        <v>48738.1496769836</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -29185,7 +29173,7 @@
         <v>2011</v>
       </c>
       <c r="C872" t="n">
-        <v>75785</v>
+        <v>75784.9680474476</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -29218,7 +29206,7 @@
         <v>2012</v>
       </c>
       <c r="C873" t="n">
-        <v>75023.89999999999</v>
+        <v>75023.89429770681</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -29251,7 +29239,7 @@
         <v>2013</v>
       </c>
       <c r="C874" t="n">
-        <v>89641.7</v>
+        <v>89641.7484895715</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -29284,7 +29272,7 @@
         <v>2014</v>
       </c>
       <c r="C875" t="n">
-        <v>117349</v>
+        <v>117349.112539642</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -29317,7 +29305,7 @@
         <v>2015</v>
       </c>
       <c r="C876" t="n">
-        <v>143403</v>
+        <v>143403.000383291</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -29350,7 +29338,7 @@
         <v>2016</v>
       </c>
       <c r="C877" t="n">
-        <v>206806</v>
+        <v>206806.3731788</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -29383,7 +29371,7 @@
         <v>2017</v>
       </c>
       <c r="C878" t="n">
-        <v>274409</v>
+        <v>274409.329754508</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -29416,7 +29404,7 @@
         <v>2018</v>
       </c>
       <c r="C879" t="n">
-        <v>350218</v>
+        <v>350218.088444299</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -29449,7 +29437,7 @@
         <v>2019</v>
       </c>
       <c r="C880" t="n">
-        <v>468411</v>
+        <v>468410.509201647</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -29482,7 +29470,7 @@
         <v>2020</v>
       </c>
       <c r="C881" t="n">
-        <v>693878</v>
+        <v>693877.557259877</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -29515,7 +29503,7 @@
         <v>2021</v>
       </c>
       <c r="C882" t="n">
-        <v>691514</v>
+        <v>691514.0790402381</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -29548,7 +29536,7 @@
         <v>2022</v>
       </c>
       <c r="C883" t="n">
-        <v>747030</v>
+        <v>747029.771867582</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -29581,7 +29569,7 @@
         <v>2023</v>
       </c>
       <c r="C884" t="n">
-        <v>864226</v>
+        <v>864225.992813542</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -29614,7 +29602,7 @@
         <v>2010</v>
       </c>
       <c r="C885" t="n">
-        <v>2524320</v>
+        <v>2524319.8817145</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -29647,7 +29635,7 @@
         <v>2011</v>
       </c>
       <c r="C886" t="n">
-        <v>3150100</v>
+        <v>3150099.82967281</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -29680,7 +29668,7 @@
         <v>2012</v>
       </c>
       <c r="C887" t="n">
-        <v>4187400</v>
+        <v>4187403.82789378</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -29713,7 +29701,7 @@
         <v>2013</v>
       </c>
       <c r="C888" t="n">
-        <v>6291850</v>
+        <v>6291850.08961455</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -29746,7 +29734,7 @@
         <v>2014</v>
       </c>
       <c r="C889" t="n">
-        <v>6646030</v>
+        <v>6646026.37200577</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -29779,7 +29767,7 @@
         <v>2015</v>
       </c>
       <c r="C890" t="n">
-        <v>6922940</v>
+        <v>6922935.73812456</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -29812,7 +29800,7 @@
         <v>2016</v>
       </c>
       <c r="C891" t="n">
-        <v>7862830</v>
+        <v>7862829.89745571</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -29845,7 +29833,7 @@
         <v>2017</v>
       </c>
       <c r="C892" t="n">
-        <v>8264960</v>
+        <v>8264958.1640134</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -29878,7 +29866,7 @@
         <v>2010</v>
       </c>
       <c r="C893" t="n">
-        <v>33441.6</v>
+        <v>33441.6478068975</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -29911,7 +29899,7 @@
         <v>2011</v>
       </c>
       <c r="C894" t="n">
-        <v>50111.1</v>
+        <v>50111.0826481304</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -29944,7 +29932,7 @@
         <v>2012</v>
       </c>
       <c r="C895" t="n">
-        <v>60495.2</v>
+        <v>60495.1526041813</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -29977,7 +29965,7 @@
         <v>2013</v>
       </c>
       <c r="C896" t="n">
-        <v>99044.2</v>
+        <v>99044.1581455509</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -30010,7 +29998,7 @@
         <v>2014</v>
       </c>
       <c r="C897" t="n">
-        <v>112428</v>
+        <v>112427.505118421</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -30043,7 +30031,7 @@
         <v>2015</v>
       </c>
       <c r="C898" t="n">
-        <v>114907</v>
+        <v>114907.147206318</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -30076,7 +30064,7 @@
         <v>2016</v>
       </c>
       <c r="C899" t="n">
-        <v>127812</v>
+        <v>127812.209475762</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -30109,7 +30097,7 @@
         <v>2017</v>
       </c>
       <c r="C900" t="n">
-        <v>134936</v>
+        <v>134936.182151732</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -30142,7 +30130,7 @@
         <v>2010</v>
       </c>
       <c r="C901" t="n">
-        <v>466391</v>
+        <v>466391.029290443</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -30175,7 +30163,7 @@
         <v>2011</v>
       </c>
       <c r="C902" t="n">
-        <v>471881</v>
+        <v>471881.125756637</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -30208,7 +30196,7 @@
         <v>2012</v>
       </c>
       <c r="C903" t="n">
-        <v>644005</v>
+        <v>644004.747500391</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -30241,7 +30229,7 @@
         <v>2013</v>
       </c>
       <c r="C904" t="n">
-        <v>230304</v>
+        <v>230303.501044043</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -30274,7 +30262,7 @@
         <v>2014</v>
       </c>
       <c r="C905" t="n">
-        <v>280165</v>
+        <v>280165.06925911</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -30307,7 +30295,7 @@
         <v>2015</v>
       </c>
       <c r="C906" t="n">
-        <v>310644</v>
+        <v>310643.854857767</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -30340,7 +30328,7 @@
         <v>2016</v>
       </c>
       <c r="C907" t="n">
-        <v>343225</v>
+        <v>343225.01331865</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -30373,7 +30361,7 @@
         <v>2017</v>
       </c>
       <c r="C908" t="n">
-        <v>332404</v>
+        <v>332404.401827351</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -30406,7 +30394,7 @@
         <v>2010</v>
       </c>
       <c r="C909" t="n">
-        <v>26548.4</v>
+        <v>26548.3929154033</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -30439,7 +30427,7 @@
         <v>2011</v>
       </c>
       <c r="C910" t="n">
-        <v>38988</v>
+        <v>38987.9636340803</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -30472,7 +30460,7 @@
         <v>2012</v>
       </c>
       <c r="C911" t="n">
-        <v>42643.9</v>
+        <v>42643.9044400232</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -30505,7 +30493,7 @@
         <v>2013</v>
       </c>
       <c r="C912" t="n">
-        <v>19962</v>
+        <v>19962.0387789822</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -30538,7 +30526,7 @@
         <v>2014</v>
       </c>
       <c r="C913" t="n">
-        <v>20797.3</v>
+        <v>20797.2964514244</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -30571,7 +30559,7 @@
         <v>2015</v>
       </c>
       <c r="C914" t="n">
-        <v>23059.2</v>
+        <v>23059.2378693662</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -30604,7 +30592,7 @@
         <v>2016</v>
       </c>
       <c r="C915" t="n">
-        <v>23531.7</v>
+        <v>23531.7249582519</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -30637,7 +30625,7 @@
         <v>2017</v>
       </c>
       <c r="C916" t="n">
-        <v>22705.2</v>
+        <v>22705.2472379701</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -30670,7 +30658,7 @@
         <v>2013</v>
       </c>
       <c r="C917" t="n">
-        <v>33876.7</v>
+        <v>33876.6798988872</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -30703,7 +30691,7 @@
         <v>2014</v>
       </c>
       <c r="C918" t="n">
-        <v>40168.9</v>
+        <v>40168.9131310012</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -30736,7 +30724,7 @@
         <v>2015</v>
       </c>
       <c r="C919" t="n">
-        <v>47770.2</v>
+        <v>47770.1794520645</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -30769,7 +30757,7 @@
         <v>2016</v>
       </c>
       <c r="C920" t="n">
-        <v>53525.2</v>
+        <v>53525.2246367968</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -30802,7 +30790,7 @@
         <v>2017</v>
       </c>
       <c r="C921" t="n">
-        <v>52861.1</v>
+        <v>52861.1452035052</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -30835,7 +30823,7 @@
         <v>2018</v>
       </c>
       <c r="C922" t="n">
-        <v>67825.8</v>
+        <v>67825.84284494761</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -30868,7 +30856,7 @@
         <v>2019</v>
       </c>
       <c r="C923" t="n">
-        <v>74176.5</v>
+        <v>74176.5004202729</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -30901,7 +30889,7 @@
         <v>2020</v>
       </c>
       <c r="C924" t="n">
-        <v>105774</v>
+        <v>105774.415100804</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -30934,7 +30922,7 @@
         <v>2021</v>
       </c>
       <c r="C925" t="n">
-        <v>166601</v>
+        <v>166601.056016946</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -30967,7 +30955,7 @@
         <v>2022</v>
       </c>
       <c r="C926" t="n">
-        <v>182547</v>
+        <v>182547.482077026</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -31000,7 +30988,7 @@
         <v>2023</v>
       </c>
       <c r="C927" t="n">
-        <v>222325</v>
+        <v>222324.675849</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -31033,7 +31021,7 @@
         <v>2010</v>
       </c>
       <c r="C928" t="n">
-        <v>53930</v>
+        <v>53929.9833029185</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -31066,7 +31054,7 @@
         <v>2011</v>
       </c>
       <c r="C929" t="n">
-        <v>146645</v>
+        <v>146645.057789607</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -31099,7 +31087,7 @@
         <v>2012</v>
       </c>
       <c r="C930" t="n">
-        <v>135587</v>
+        <v>135586.672549375</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -31132,7 +31120,7 @@
         <v>2013</v>
       </c>
       <c r="C931" t="n">
-        <v>36557.7</v>
+        <v>36557.7161485882</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -31165,7 +31153,7 @@
         <v>2014</v>
       </c>
       <c r="C932" t="n">
-        <v>42135.7</v>
+        <v>42135.6645309098</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -31198,7 +31186,7 @@
         <v>2015</v>
       </c>
       <c r="C933" t="n">
-        <v>45574.7</v>
+        <v>45574.7082350173</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -31231,7 +31219,7 @@
         <v>2016</v>
       </c>
       <c r="C934" t="n">
-        <v>49285.7</v>
+        <v>49285.6688423534</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -31264,7 +31252,7 @@
         <v>2017</v>
       </c>
       <c r="C935" t="n">
-        <v>49795</v>
+        <v>49795.0118010153</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -31297,7 +31285,7 @@
         <v>2010</v>
       </c>
       <c r="C936" t="n">
-        <v>236955</v>
+        <v>236955.347470848</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -31330,7 +31318,7 @@
         <v>2011</v>
       </c>
       <c r="C937" t="n">
-        <v>239560</v>
+        <v>239559.859909905</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -31363,7 +31351,7 @@
         <v>2012</v>
       </c>
       <c r="C938" t="n">
-        <v>338209</v>
+        <v>338208.921394556</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -31396,7 +31384,7 @@
         <v>2013</v>
       </c>
       <c r="C939" t="n">
-        <v>41759.1</v>
+        <v>41759.0986993677</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -31429,7 +31417,7 @@
         <v>2014</v>
       </c>
       <c r="C940" t="n">
-        <v>51273.5</v>
+        <v>51273.5370521665</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -31462,7 +31450,7 @@
         <v>2015</v>
       </c>
       <c r="C941" t="n">
-        <v>59689.2</v>
+        <v>59689.1949576398</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -31495,7 +31483,7 @@
         <v>2016</v>
       </c>
       <c r="C942" t="n">
-        <v>67443.7</v>
+        <v>67443.6584224735</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -31528,7 +31516,7 @@
         <v>2017</v>
       </c>
       <c r="C943" t="n">
-        <v>68416.7</v>
+        <v>68416.6945695683</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -31561,7 +31549,7 @@
         <v>2010</v>
       </c>
       <c r="C944" t="n">
-        <v>74030.8</v>
+        <v>74030.81157416941</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -31594,7 +31582,7 @@
         <v>2011</v>
       </c>
       <c r="C945" t="n">
-        <v>90273.39999999999</v>
+        <v>90273.39570263861</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -31627,7 +31615,7 @@
         <v>2012</v>
       </c>
       <c r="C946" t="n">
-        <v>99262.2</v>
+        <v>99262.2165411004</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -31660,7 +31648,7 @@
         <v>2013</v>
       </c>
       <c r="C947" t="n">
-        <v>76947.2</v>
+        <v>76947.2246917735</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -31693,7 +31681,7 @@
         <v>2014</v>
       </c>
       <c r="C948" t="n">
-        <v>91616.60000000001</v>
+        <v>91616.59817598941</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -31726,7 +31714,7 @@
         <v>2015</v>
       </c>
       <c r="C949" t="n">
-        <v>106256</v>
+        <v>106256.258725358</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -31759,7 +31747,7 @@
         <v>2016</v>
       </c>
       <c r="C950" t="n">
-        <v>125297</v>
+        <v>125296.713682525</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -31792,7 +31780,7 @@
         <v>2017</v>
       </c>
       <c r="C951" t="n">
-        <v>126661</v>
+        <v>126661.022076284</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -31825,7 +31813,7 @@
         <v>2018</v>
       </c>
       <c r="C952" t="n">
-        <v>153374</v>
+        <v>153373.953113786</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -31858,7 +31846,7 @@
         <v>2019</v>
       </c>
       <c r="C953" t="n">
-        <v>190585</v>
+        <v>190584.882853231</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -31891,7 +31879,7 @@
         <v>2020</v>
       </c>
       <c r="C954" t="n">
-        <v>287100</v>
+        <v>287100.359172196</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -31924,7 +31912,7 @@
         <v>2021</v>
       </c>
       <c r="C955" t="n">
-        <v>416486</v>
+        <v>416486.341819414</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -31957,7 +31945,7 @@
         <v>2022</v>
       </c>
       <c r="C956" t="n">
-        <v>451752</v>
+        <v>451751.577460956</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -31990,7 +31978,7 @@
         <v>2023</v>
       </c>
       <c r="C957" t="n">
-        <v>493335</v>
+        <v>493334.559397572</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -32023,7 +32011,7 @@
         <v>2010</v>
       </c>
       <c r="C958" t="n">
-        <v>65409</v>
+        <v>65408.9959244048</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -32056,7 +32044,7 @@
         <v>2011</v>
       </c>
       <c r="C959" t="n">
-        <v>81084.89999999999</v>
+        <v>81084.865333569</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -32089,7 +32077,7 @@
         <v>2012</v>
       </c>
       <c r="C960" t="n">
-        <v>90621.7</v>
+        <v>90621.6907416688</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -32122,7 +32110,7 @@
         <v>2013</v>
       </c>
       <c r="C961" t="n">
-        <v>47497.6</v>
+        <v>47497.6142285067</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -32155,7 +32143,7 @@
         <v>2014</v>
       </c>
       <c r="C962" t="n">
-        <v>52516.2</v>
+        <v>52516.1857425136</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -32188,7 +32176,7 @@
         <v>2015</v>
       </c>
       <c r="C963" t="n">
-        <v>56506.4</v>
+        <v>56506.3738888275</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -32221,7 +32209,7 @@
         <v>2016</v>
       </c>
       <c r="C964" t="n">
-        <v>61577</v>
+        <v>61576.9656582263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -32254,7 +32242,7 @@
         <v>2017</v>
       </c>
       <c r="C965" t="n">
-        <v>59773</v>
+        <v>59773.0271390388</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -32287,7 +32275,7 @@
         <v>2010</v>
       </c>
       <c r="C966" t="n">
-        <v>30557.9</v>
+        <v>30557.8830125923</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -32320,7 +32308,7 @@
         <v>2011</v>
       </c>
       <c r="C967" t="n">
-        <v>38999.8</v>
+        <v>38999.8108975418</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -32353,7 +32341,7 @@
         <v>2012</v>
       </c>
       <c r="C968" t="n">
-        <v>40198.8</v>
+        <v>40198.7913557593</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -32386,7 +32374,7 @@
         <v>2013</v>
       </c>
       <c r="C969" t="n">
-        <v>51086.2</v>
+        <v>51086.2371119167</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -32419,7 +32407,7 @@
         <v>2014</v>
       </c>
       <c r="C970" t="n">
-        <v>58674.4</v>
+        <v>58674.3578006249</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -32452,7 +32440,7 @@
         <v>2015</v>
       </c>
       <c r="C971" t="n">
-        <v>72394.60000000001</v>
+        <v>72394.646029414</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -32485,7 +32473,7 @@
         <v>2016</v>
       </c>
       <c r="C972" t="n">
-        <v>79417.10000000001</v>
+        <v>79417.1420287799</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -32518,7 +32506,7 @@
         <v>2017</v>
       </c>
       <c r="C973" t="n">
-        <v>73625</v>
+        <v>73625.04384610429</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -32551,7 +32539,7 @@
         <v>2010</v>
       </c>
       <c r="C974" t="n">
-        <v>87200.5</v>
+        <v>87200.51979643571</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -32584,7 +32572,7 @@
         <v>2011</v>
       </c>
       <c r="C975" t="n">
-        <v>107590</v>
+        <v>107589.729986893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -32617,7 +32605,7 @@
         <v>2012</v>
       </c>
       <c r="C976" t="n">
-        <v>118950</v>
+        <v>118949.566866168</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -32650,7 +32638,7 @@
         <v>2013</v>
       </c>
       <c r="C977" t="n">
-        <v>154470</v>
+        <v>154470.406730921</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -32683,7 +32671,7 @@
         <v>2014</v>
       </c>
       <c r="C978" t="n">
-        <v>109733</v>
+        <v>109733.147576593</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -32716,7 +32704,7 @@
         <v>2015</v>
       </c>
       <c r="C979" t="n">
-        <v>147179</v>
+        <v>147179.412781171</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -32749,7 +32737,7 @@
         <v>2016</v>
       </c>
       <c r="C980" t="n">
-        <v>151896</v>
+        <v>151896.154261904</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -32782,7 +32770,7 @@
         <v>2017</v>
       </c>
       <c r="C981" t="n">
-        <v>223646</v>
+        <v>223645.873113298</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -32815,7 +32803,7 @@
         <v>2018</v>
       </c>
       <c r="C982" t="n">
-        <v>321771</v>
+        <v>321770.543563246</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -32848,7 +32836,7 @@
         <v>2019</v>
       </c>
       <c r="C983" t="n">
-        <v>330198</v>
+        <v>330197.89919308</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -32881,7 +32869,7 @@
         <v>2020</v>
       </c>
       <c r="C984" t="n">
-        <v>423092</v>
+        <v>423092.045198861</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -32914,7 +32902,7 @@
         <v>2021</v>
       </c>
       <c r="C985" t="n">
-        <v>416536</v>
+        <v>416536.292807024</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -32947,7 +32935,7 @@
         <v>2022</v>
       </c>
       <c r="C986" t="n">
-        <v>507900</v>
+        <v>507900.02979926</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -32980,7 +32968,7 @@
         <v>2023</v>
       </c>
       <c r="C987" t="n">
-        <v>610216</v>
+        <v>610216.006063475</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -33013,7 +33001,7 @@
         <v>2010</v>
       </c>
       <c r="C988" t="n">
-        <v>23854.9</v>
+        <v>23854.8747663206</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -33046,7 +33034,7 @@
         <v>2011</v>
       </c>
       <c r="C989" t="n">
-        <v>20501.5</v>
+        <v>20501.5195739429</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -33079,7 +33067,7 @@
         <v>2012</v>
       </c>
       <c r="C990" t="n">
-        <v>35255.9</v>
+        <v>35255.8728592762</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -33112,7 +33100,7 @@
         <v>2013</v>
       </c>
       <c r="C991" t="n">
-        <v>67384.10000000001</v>
+        <v>67384.0750555768</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -33145,7 +33133,7 @@
         <v>2014</v>
       </c>
       <c r="C992" t="n">
-        <v>100527</v>
+        <v>100527.011405809</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -33178,7 +33166,7 @@
         <v>2015</v>
       </c>
       <c r="C993" t="n">
-        <v>109356</v>
+        <v>109355.948793854</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -33211,7 +33199,7 @@
         <v>2016</v>
       </c>
       <c r="C994" t="n">
-        <v>98259.7</v>
+        <v>98259.6798499127</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -33244,7 +33232,7 @@
         <v>2017</v>
       </c>
       <c r="C995" t="n">
-        <v>110629</v>
+        <v>110629.258025946</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -33277,7 +33265,7 @@
         <v>2018</v>
       </c>
       <c r="C996" t="n">
-        <v>135376</v>
+        <v>135376.414175783</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -33310,7 +33298,7 @@
         <v>2019</v>
       </c>
       <c r="C997" t="n">
-        <v>131325</v>
+        <v>131325.067567638</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -33343,7 +33331,7 @@
         <v>2020</v>
       </c>
       <c r="C998" t="n">
-        <v>188802</v>
+        <v>188802.296442677</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -33376,7 +33364,7 @@
         <v>2021</v>
       </c>
       <c r="C999" t="n">
-        <v>202786</v>
+        <v>202785.600177036</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -33409,7 +33397,7 @@
         <v>2022</v>
       </c>
       <c r="C1000" t="n">
-        <v>202154</v>
+        <v>202153.528399156</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -33442,7 +33430,7 @@
         <v>2023</v>
       </c>
       <c r="C1001" t="n">
-        <v>234720</v>
+        <v>234719.643147641</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -33475,7 +33463,7 @@
         <v>2010</v>
       </c>
       <c r="C1002" t="n">
-        <v>12248.4</v>
+        <v>12248.3863233054</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -33508,7 +33496,7 @@
         <v>2011</v>
       </c>
       <c r="C1003" t="n">
-        <v>12442.9</v>
+        <v>12442.9113407951</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -33541,7 +33529,7 @@
         <v>2012</v>
       </c>
       <c r="C1004" t="n">
-        <v>12059.6</v>
+        <v>12059.5955982099</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -33574,7 +33562,7 @@
         <v>2013</v>
       </c>
       <c r="C1005" t="n">
-        <v>11865.8</v>
+        <v>11865.8382132422</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -33607,7 +33595,7 @@
         <v>2014</v>
       </c>
       <c r="C1006" t="n">
-        <v>15006.9</v>
+        <v>15006.9242947052</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -33640,7 +33628,7 @@
         <v>2015</v>
       </c>
       <c r="C1007" t="n">
-        <v>41555.7</v>
+        <v>41555.692043586</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -33673,7 +33661,7 @@
         <v>2016</v>
       </c>
       <c r="C1008" t="n">
-        <v>52680</v>
+        <v>52680.0189266529</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -33706,7 +33694,7 @@
         <v>2017</v>
       </c>
       <c r="C1009" t="n">
-        <v>77873.3</v>
+        <v>77873.2771588824</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -33739,7 +33727,7 @@
         <v>2018</v>
       </c>
       <c r="C1010" t="n">
-        <v>96499</v>
+        <v>96498.95547439771</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -33772,7 +33760,7 @@
         <v>2019</v>
       </c>
       <c r="C1011" t="n">
-        <v>70529</v>
+        <v>70528.99820148719</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -33805,7 +33793,7 @@
         <v>2020</v>
       </c>
       <c r="C1012" t="n">
-        <v>64715.3</v>
+        <v>64715.313008995</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -33838,7 +33826,7 @@
         <v>2021</v>
       </c>
       <c r="C1013" t="n">
-        <v>72767.5</v>
+        <v>72767.4660327522</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -33871,7 +33859,7 @@
         <v>2022</v>
       </c>
       <c r="C1014" t="n">
-        <v>96707.2</v>
+        <v>96707.2084617575</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -33904,7 +33892,7 @@
         <v>2023</v>
       </c>
       <c r="C1015" t="n">
-        <v>133328</v>
+        <v>133328.243281628</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -33937,7 +33925,7 @@
         <v>2010</v>
       </c>
       <c r="C1016" t="n">
-        <v>123825</v>
+        <v>123824.506615636</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -33970,7 +33958,7 @@
         <v>2011</v>
       </c>
       <c r="C1017" t="n">
-        <v>169248</v>
+        <v>169248.161334754</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -34003,7 +33991,7 @@
         <v>2012</v>
       </c>
       <c r="C1018" t="n">
-        <v>145101</v>
+        <v>145100.67568548</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -34036,7 +34024,7 @@
         <v>2013</v>
       </c>
       <c r="C1019" t="n">
-        <v>194523</v>
+        <v>194522.651650883</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -34069,7 +34057,7 @@
         <v>2014</v>
       </c>
       <c r="C1020" t="n">
-        <v>225472</v>
+        <v>225472.268538029</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -34102,7 +34090,7 @@
         <v>2010</v>
       </c>
       <c r="C1021" t="n">
-        <v>170296</v>
+        <v>170295.712173484</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -34135,7 +34123,7 @@
         <v>2011</v>
       </c>
       <c r="C1022" t="n">
-        <v>205689</v>
+        <v>205688.64292589</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -34168,7 +34156,7 @@
         <v>2012</v>
       </c>
       <c r="C1023" t="n">
-        <v>241746</v>
+        <v>241745.738636364</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -34201,7 +34189,7 @@
         <v>2013</v>
       </c>
       <c r="C1024" t="n">
-        <v>328730</v>
+        <v>328730.474040632</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -34234,7 +34222,7 @@
         <v>2014</v>
       </c>
       <c r="C1025" t="n">
-        <v>139890</v>
+        <v>139889.783806698</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -34267,7 +34255,7 @@
         <v>2010</v>
       </c>
       <c r="C1026" t="n">
-        <v>82608.7</v>
+        <v>82608.6956521739</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -34300,7 +34288,7 @@
         <v>2011</v>
       </c>
       <c r="C1027" t="n">
-        <v>65395</v>
+        <v>65394.9804078748</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -34333,7 +34321,7 @@
         <v>2012</v>
       </c>
       <c r="C1028" t="n">
-        <v>73406.8</v>
+        <v>73406.8182439371</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -34366,7 +34354,7 @@
         <v>2013</v>
       </c>
       <c r="C1029" t="n">
-        <v>89187.8</v>
+        <v>89187.8170689266</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -34399,7 +34387,7 @@
         <v>2014</v>
       </c>
       <c r="C1030" t="n">
-        <v>98521.10000000001</v>
+        <v>98521.129357716</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -34432,7 +34420,7 @@
         <v>2010</v>
       </c>
       <c r="C1031" t="n">
-        <v>187883</v>
+        <v>187882.73487539</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -34465,7 +34453,7 @@
         <v>2011</v>
       </c>
       <c r="C1032" t="n">
-        <v>223109</v>
+        <v>223108.790171498</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -34498,7 +34486,7 @@
         <v>2012</v>
       </c>
       <c r="C1033" t="n">
-        <v>232785</v>
+        <v>232784.554016693</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -34531,7 +34519,7 @@
         <v>2013</v>
       </c>
       <c r="C1034" t="n">
-        <v>240876</v>
+        <v>240875.971653087</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -34564,7 +34552,7 @@
         <v>2014</v>
       </c>
       <c r="C1035" t="n">
-        <v>259274</v>
+        <v>259273.968070909</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -34597,7 +34585,7 @@
         <v>2010</v>
       </c>
       <c r="C1036" t="n">
-        <v>40218.8</v>
+        <v>40218.7660762512</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -34630,7 +34618,7 @@
         <v>2011</v>
       </c>
       <c r="C1037" t="n">
-        <v>95362.3</v>
+        <v>95362.3387422852</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -34663,7 +34651,7 @@
         <v>2012</v>
       </c>
       <c r="C1038" t="n">
-        <v>138288</v>
+        <v>138288.267820913</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -34696,7 +34684,7 @@
         <v>2013</v>
       </c>
       <c r="C1039" t="n">
-        <v>172526</v>
+        <v>172526.095433703</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -34729,7 +34717,7 @@
         <v>2014</v>
       </c>
       <c r="C1040" t="n">
-        <v>291691</v>
+        <v>291691.051864755</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -34762,7 +34750,7 @@
         <v>2010</v>
       </c>
       <c r="C1041" t="n">
-        <v>213731</v>
+        <v>213730.581850727</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -34795,7 +34783,7 @@
         <v>2011</v>
       </c>
       <c r="C1042" t="n">
-        <v>206423</v>
+        <v>206423.123309237</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -34828,7 +34816,7 @@
         <v>2012</v>
       </c>
       <c r="C1043" t="n">
-        <v>262472</v>
+        <v>262472.325401224</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -34861,7 +34849,7 @@
         <v>2013</v>
       </c>
       <c r="C1044" t="n">
-        <v>295988</v>
+        <v>295987.552440642</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -34894,7 +34882,7 @@
         <v>2014</v>
       </c>
       <c r="C1045" t="n">
-        <v>362900</v>
+        <v>362900.257885635</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -34927,7 +34915,7 @@
         <v>2010</v>
       </c>
       <c r="C1046" t="n">
-        <v>156102</v>
+        <v>156102.200420752</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -34960,7 +34948,7 @@
         <v>2011</v>
       </c>
       <c r="C1047" t="n">
-        <v>164334</v>
+        <v>164334.232011356</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -34993,7 +34981,7 @@
         <v>2014</v>
       </c>
       <c r="C1048" t="n">
-        <v>110832</v>
+        <v>110832.433674998</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -35026,7 +35014,7 @@
         <v>2010</v>
       </c>
       <c r="C1049" t="n">
-        <v>102604</v>
+        <v>102604.351125727</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -35059,7 +35047,7 @@
         <v>2011</v>
       </c>
       <c r="C1050" t="n">
-        <v>118235</v>
+        <v>118235.185583541</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -35092,7 +35080,7 @@
         <v>2012</v>
       </c>
       <c r="C1051" t="n">
-        <v>132112</v>
+        <v>132111.800797041</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -35125,7 +35113,7 @@
         <v>2013</v>
       </c>
       <c r="C1052" t="n">
-        <v>82192.39999999999</v>
+        <v>82192.36630178741</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -35158,7 +35146,7 @@
         <v>2014</v>
       </c>
       <c r="C1053" t="n">
-        <v>87918.60000000001</v>
+        <v>87918.57441519439</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -35191,7 +35179,7 @@
         <v>2010</v>
       </c>
       <c r="C1054" t="n">
-        <v>219871</v>
+        <v>219870.639257508</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -35224,7 +35212,7 @@
         <v>2011</v>
       </c>
       <c r="C1055" t="n">
-        <v>242805</v>
+        <v>242805.001580059</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -35257,7 +35245,7 @@
         <v>2012</v>
       </c>
       <c r="C1056" t="n">
-        <v>273554</v>
+        <v>273554.16291994</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -35290,7 +35278,7 @@
         <v>2013</v>
       </c>
       <c r="C1057" t="n">
-        <v>135162</v>
+        <v>135161.904019095</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -35323,7 +35311,7 @@
         <v>2014</v>
       </c>
       <c r="C1058" t="n">
-        <v>150092</v>
+        <v>150091.555849068</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -35356,7 +35344,7 @@
         <v>2010</v>
       </c>
       <c r="C1059" t="n">
-        <v>92748.2</v>
+        <v>92748.2306065477</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -35389,7 +35377,7 @@
         <v>2011</v>
       </c>
       <c r="C1060" t="n">
-        <v>120043</v>
+        <v>120043.242350633</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -35422,7 +35410,7 @@
         <v>2014</v>
       </c>
       <c r="C1061" t="n">
-        <v>54542.4</v>
+        <v>54542.3789219574</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -35455,7 +35443,7 @@
         <v>2010</v>
       </c>
       <c r="C1062" t="n">
-        <v>73727.2</v>
+        <v>73727.1646135254</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -35488,7 +35476,7 @@
         <v>2011</v>
       </c>
       <c r="C1063" t="n">
-        <v>78789.3</v>
+        <v>78789.2922200301</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -35521,7 +35509,7 @@
         <v>2012</v>
       </c>
       <c r="C1064" t="n">
-        <v>82135.3</v>
+        <v>82135.2737538254</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -35554,7 +35542,7 @@
         <v>2013</v>
       </c>
       <c r="C1065" t="n">
-        <v>87820.7</v>
+        <v>87820.72861931181</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -35587,7 +35575,7 @@
         <v>2014</v>
       </c>
       <c r="C1066" t="n">
-        <v>106736</v>
+        <v>106735.955192462</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -35620,7 +35608,7 @@
         <v>2010</v>
       </c>
       <c r="C1067" t="n">
-        <v>164034</v>
+        <v>164034.306603553</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -35653,7 +35641,7 @@
         <v>2011</v>
       </c>
       <c r="C1068" t="n">
-        <v>173546</v>
+        <v>173546.089938019</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -35686,7 +35674,7 @@
         <v>2012</v>
       </c>
       <c r="C1069" t="n">
-        <v>185709</v>
+        <v>185708.92410342</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -35719,7 +35707,7 @@
         <v>2013</v>
       </c>
       <c r="C1070" t="n">
-        <v>78187.7</v>
+        <v>78187.6503608661</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -35752,7 +35740,7 @@
         <v>2014</v>
       </c>
       <c r="C1071" t="n">
-        <v>82791</v>
+        <v>82791.0200623821</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -35785,7 +35773,7 @@
         <v>2010</v>
       </c>
       <c r="C1072" t="n">
-        <v>206491</v>
+        <v>206490.506948522</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -35818,7 +35806,7 @@
         <v>2011</v>
       </c>
       <c r="C1073" t="n">
-        <v>247340</v>
+        <v>247339.963492163</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -35851,7 +35839,7 @@
         <v>2012</v>
       </c>
       <c r="C1074" t="n">
-        <v>289701</v>
+        <v>289701.228080895</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -35884,7 +35872,7 @@
         <v>2013</v>
       </c>
       <c r="C1075" t="n">
-        <v>152448</v>
+        <v>152448.137741376</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -35917,7 +35905,7 @@
         <v>2014</v>
       </c>
       <c r="C1076" t="n">
-        <v>173443</v>
+        <v>173443.275518908</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -35950,7 +35938,7 @@
         <v>2010</v>
       </c>
       <c r="C1077" t="n">
-        <v>69471.3</v>
+        <v>69471.3407779027</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -35983,7 +35971,7 @@
         <v>2011</v>
       </c>
       <c r="C1078" t="n">
-        <v>121819</v>
+        <v>121819.446525527</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -36016,7 +36004,7 @@
         <v>2014</v>
       </c>
       <c r="C1079" t="n">
-        <v>174267</v>
+        <v>174267.308942036</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -36049,7 +36037,7 @@
         <v>2010</v>
       </c>
       <c r="C1080" t="n">
-        <v>192081</v>
+        <v>192080.640756374</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -36082,7 +36070,7 @@
         <v>2011</v>
       </c>
       <c r="C1081" t="n">
-        <v>224244</v>
+        <v>224243.826797072</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -36115,7 +36103,7 @@
         <v>2014</v>
       </c>
       <c r="C1082" t="n">
-        <v>115963</v>
+        <v>115962.644566764</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -36148,7 +36136,7 @@
         <v>2010</v>
       </c>
       <c r="C1083" t="n">
-        <v>367515</v>
+        <v>367514.615263075</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -36181,7 +36169,7 @@
         <v>2011</v>
       </c>
       <c r="C1084" t="n">
-        <v>384733</v>
+        <v>384733.349779402</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -36214,7 +36202,7 @@
         <v>2014</v>
       </c>
       <c r="C1085" t="n">
-        <v>226244</v>
+        <v>226244.343891403</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -36247,7 +36235,7 @@
         <v>2010</v>
       </c>
       <c r="C1086" t="n">
-        <v>68423</v>
+        <v>68423.0234765614</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -36280,7 +36268,7 @@
         <v>2011</v>
       </c>
       <c r="C1087" t="n">
-        <v>71986.2</v>
+        <v>71986.2158007422</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -36313,7 +36301,7 @@
         <v>2014</v>
       </c>
       <c r="C1088" t="n">
-        <v>152364</v>
+        <v>152363.926316805</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -36346,7 +36334,7 @@
         <v>2010</v>
       </c>
       <c r="C1089" t="n">
-        <v>153122</v>
+        <v>153122.496925683</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -36379,7 +36367,7 @@
         <v>2011</v>
       </c>
       <c r="C1090" t="n">
-        <v>156403</v>
+        <v>156402.76034487</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -36412,7 +36400,7 @@
         <v>2012</v>
       </c>
       <c r="C1091" t="n">
-        <v>185452</v>
+        <v>185452.181377574</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -36445,7 +36433,7 @@
         <v>2013</v>
       </c>
       <c r="C1092" t="n">
-        <v>58831.6</v>
+        <v>58831.6057799994</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -36478,7 +36466,7 @@
         <v>2014</v>
       </c>
       <c r="C1093" t="n">
-        <v>62613.7</v>
+        <v>62613.7308850715</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -36511,7 +36499,7 @@
         <v>2010</v>
       </c>
       <c r="C1094" t="n">
-        <v>231967</v>
+        <v>231967.112985378</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -36544,7 +36532,7 @@
         <v>2011</v>
       </c>
       <c r="C1095" t="n">
-        <v>283492</v>
+        <v>283492.357097498</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -36577,7 +36565,7 @@
         <v>2012</v>
       </c>
       <c r="C1096" t="n">
-        <v>285776</v>
+        <v>285776.39608166</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -36610,7 +36598,7 @@
         <v>2013</v>
       </c>
       <c r="C1097" t="n">
-        <v>191699</v>
+        <v>191698.817084555</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -36643,7 +36631,7 @@
         <v>2014</v>
       </c>
       <c r="C1098" t="n">
-        <v>206553</v>
+        <v>206552.808403204</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -36676,7 +36664,7 @@
         <v>2010</v>
       </c>
       <c r="C1099" t="n">
-        <v>158791</v>
+        <v>158791.191115942</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -36709,7 +36697,7 @@
         <v>2011</v>
       </c>
       <c r="C1100" t="n">
-        <v>235264</v>
+        <v>235263.610564394</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -36742,7 +36730,7 @@
         <v>2012</v>
       </c>
       <c r="C1101" t="n">
-        <v>235399</v>
+        <v>235398.755280687</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -36775,7 +36763,7 @@
         <v>2013</v>
       </c>
       <c r="C1102" t="n">
-        <v>273322</v>
+        <v>273322.412401681</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -36808,7 +36796,7 @@
         <v>2014</v>
       </c>
       <c r="C1103" t="n">
-        <v>309638</v>
+        <v>309637.68124979</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -36841,7 +36829,7 @@
         <v>2010</v>
       </c>
       <c r="C1104" t="n">
-        <v>6893950</v>
+        <v>6893946.59317685</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -36874,7 +36862,7 @@
         <v>2011</v>
       </c>
       <c r="C1105" t="n">
-        <v>8663880</v>
+        <v>8663882.2288855</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -36907,7 +36895,7 @@
         <v>2014</v>
       </c>
       <c r="C1106" t="n">
-        <v>18736600</v>
+        <v>18736616.7023555</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -36940,7 +36928,7 @@
         <v>2010</v>
       </c>
       <c r="C1107" t="n">
-        <v>110376</v>
+        <v>110376.291172656</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
@@ -36973,7 +36961,7 @@
         <v>2011</v>
       </c>
       <c r="C1108" t="n">
-        <v>157404</v>
+        <v>157403.885252568</v>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
@@ -37006,7 +36994,7 @@
         <v>2012</v>
       </c>
       <c r="C1109" t="n">
-        <v>189020</v>
+        <v>189019.639140507</v>
       </c>
       <c r="D1109" t="inlineStr">
         <is>
@@ -37039,7 +37027,7 @@
         <v>2013</v>
       </c>
       <c r="C1110" t="n">
-        <v>311203</v>
+        <v>311203.319502075</v>
       </c>
       <c r="D1110" t="inlineStr">
         <is>
@@ -37072,7 +37060,7 @@
         <v>2014</v>
       </c>
       <c r="C1111" t="n">
-        <v>336634</v>
+        <v>336633.663366337</v>
       </c>
       <c r="D1111" t="inlineStr">
         <is>
@@ -37105,7 +37093,7 @@
         <v>2010</v>
       </c>
       <c r="C1112" t="n">
-        <v>1024390</v>
+        <v>1024391.85343441</v>
       </c>
       <c r="D1112" t="inlineStr">
         <is>
@@ -37138,7 +37126,7 @@
         <v>2011</v>
       </c>
       <c r="C1113" t="n">
-        <v>1088890</v>
+        <v>1088888.53381056</v>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
@@ -37171,7 +37159,7 @@
         <v>2014</v>
       </c>
       <c r="C1114" t="n">
-        <v>587238</v>
+        <v>587237.804918282</v>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
@@ -37204,7 +37192,7 @@
         <v>2010</v>
       </c>
       <c r="C1115" t="n">
-        <v>127060</v>
+        <v>127060.264552483</v>
       </c>
       <c r="D1115" t="inlineStr">
         <is>
@@ -37237,7 +37225,7 @@
         <v>2011</v>
       </c>
       <c r="C1116" t="n">
-        <v>164140</v>
+        <v>164139.943194743</v>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
@@ -37270,7 +37258,7 @@
         <v>2014</v>
       </c>
       <c r="C1117" t="n">
-        <v>73266.60000000001</v>
+        <v>73266.6155551384</v>
       </c>
       <c r="D1117" t="inlineStr">
         <is>
@@ -37303,7 +37291,7 @@
         <v>2014</v>
       </c>
       <c r="C1118" t="n">
-        <v>99137.10000000001</v>
+        <v>99137.066908708</v>
       </c>
       <c r="D1118" t="inlineStr">
         <is>
@@ -37336,7 +37324,7 @@
         <v>2010</v>
       </c>
       <c r="C1119" t="n">
-        <v>147651</v>
+        <v>147651.006711409</v>
       </c>
       <c r="D1119" t="inlineStr">
         <is>
@@ -37369,7 +37357,7 @@
         <v>2011</v>
       </c>
       <c r="C1120" t="n">
-        <v>364695</v>
+        <v>364695.065890285</v>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
@@ -37402,7 +37390,7 @@
         <v>2014</v>
       </c>
       <c r="C1121" t="n">
-        <v>113523</v>
+        <v>113522.954091816</v>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
@@ -37435,7 +37423,7 @@
         <v>2010</v>
       </c>
       <c r="C1122" t="n">
-        <v>667399</v>
+        <v>667399.248575186</v>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
@@ -37468,7 +37456,7 @@
         <v>2011</v>
       </c>
       <c r="C1123" t="n">
-        <v>694275</v>
+        <v>694274.7787495051</v>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
@@ -37501,7 +37489,7 @@
         <v>2014</v>
       </c>
       <c r="C1124" t="n">
-        <v>140184</v>
+        <v>140183.726010298</v>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
@@ -37534,7 +37522,7 @@
         <v>2010</v>
       </c>
       <c r="C1125" t="n">
-        <v>226705</v>
+        <v>226705.237189458</v>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
@@ -37567,7 +37555,7 @@
         <v>2011</v>
       </c>
       <c r="C1126" t="n">
-        <v>255404</v>
+        <v>255404.011508325</v>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
@@ -37600,7 +37588,7 @@
         <v>2014</v>
       </c>
       <c r="C1127" t="n">
-        <v>244970</v>
+        <v>244970.394874131</v>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
@@ -37633,7 +37621,7 @@
         <v>2010</v>
       </c>
       <c r="C1128" t="n">
-        <v>307865</v>
+        <v>307864.705882353</v>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
@@ -37666,7 +37654,7 @@
         <v>2011</v>
       </c>
       <c r="C1129" t="n">
-        <v>359473</v>
+        <v>359473.274209013</v>
       </c>
       <c r="D1129" t="inlineStr">
         <is>
@@ -37699,7 +37687,7 @@
         <v>2012</v>
       </c>
       <c r="C1130" t="n">
-        <v>399977</v>
+        <v>399976.54583002</v>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
@@ -37732,7 +37720,7 @@
         <v>2013</v>
       </c>
       <c r="C1131" t="n">
-        <v>203259</v>
+        <v>203258.731885252</v>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
@@ -37765,7 +37753,7 @@
         <v>2014</v>
       </c>
       <c r="C1132" t="n">
-        <v>136903</v>
+        <v>136903.144030789</v>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
@@ -37798,7 +37786,7 @@
         <v>2010</v>
       </c>
       <c r="C1133" t="n">
-        <v>110352</v>
+        <v>110352.283050313</v>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
@@ -37831,7 +37819,7 @@
         <v>2011</v>
       </c>
       <c r="C1134" t="n">
-        <v>161002</v>
+        <v>161002.285608993</v>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
@@ -37864,7 +37852,7 @@
         <v>2014</v>
       </c>
       <c r="C1135" t="n">
-        <v>291511</v>
+        <v>291511.3766688</v>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
@@ -37897,7 +37885,7 @@
         <v>2010</v>
       </c>
       <c r="C1136" t="n">
-        <v>349355</v>
+        <v>349355.365020608</v>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
@@ -37930,7 +37918,7 @@
         <v>2011</v>
       </c>
       <c r="C1137" t="n">
-        <v>345650</v>
+        <v>345650.086313958</v>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
@@ -37963,7 +37951,7 @@
         <v>2014</v>
       </c>
       <c r="C1138" t="n">
-        <v>482644</v>
+        <v>482644.173646638</v>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
@@ -37996,7 +37984,7 @@
         <v>2010</v>
       </c>
       <c r="C1139" t="n">
-        <v>140853</v>
+        <v>140853.005803144</v>
       </c>
       <c r="D1139" t="inlineStr">
         <is>
@@ -38029,7 +38017,7 @@
         <v>2011</v>
       </c>
       <c r="C1140" t="n">
-        <v>106364</v>
+        <v>106363.968992776</v>
       </c>
       <c r="D1140" t="inlineStr">
         <is>
@@ -38062,7 +38050,7 @@
         <v>2014</v>
       </c>
       <c r="C1141" t="n">
-        <v>356374</v>
+        <v>356374.261213846</v>
       </c>
       <c r="D1141" t="inlineStr">
         <is>
@@ -38095,7 +38083,7 @@
         <v>2010</v>
       </c>
       <c r="C1142" t="n">
-        <v>72003.2</v>
+        <v>72003.1566183861</v>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
@@ -38128,7 +38116,7 @@
         <v>2011</v>
       </c>
       <c r="C1143" t="n">
-        <v>66958.89999999999</v>
+        <v>66958.8751980309</v>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
@@ -38161,7 +38149,7 @@
         <v>2012</v>
       </c>
       <c r="C1144" t="n">
-        <v>62626.3</v>
+        <v>62626.2702173257</v>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
@@ -38194,7 +38182,7 @@
         <v>2013</v>
       </c>
       <c r="C1145" t="n">
-        <v>59101.9</v>
+        <v>59101.8644274152</v>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
@@ -38227,7 +38215,7 @@
         <v>2014</v>
       </c>
       <c r="C1146" t="n">
-        <v>54566.1</v>
+        <v>54566.0904487515</v>
       </c>
       <c r="D1146" t="inlineStr">
         <is>
